--- a/static/excel_files/IOS_TVOS.xlsx
+++ b/static/excel_files/IOS_TVOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesusalberca/Desktop/qc_matrix_generator/static/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2FED815-1E05-7746-A9A2-940AA2A701A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1ABCAF-F4F0-8347-9D37-915B85C1B9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20620" yWindow="660" windowWidth="30420" windowHeight="20780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1067,8 +1067,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1079,7 +1079,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF7F6000"/>
@@ -1127,6 +1127,25 @@
           <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF7F6000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1218,7 +1237,7 @@
     <tableColumn id="8" xr3:uid="{82D1D2EC-8C5B-6449-B66C-DD38747442A6}" name="Columna2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3"/>
     <tableColumn id="9" xr3:uid="{0DCC180D-B292-5141-B162-6BA40A619298}" name="Columna3"/>
-    <tableColumn id="10" xr3:uid="{0894BC58-29DD-1A47-A7FA-3918C47C1800}" name="Columna4"/>
+    <tableColumn id="10" xr3:uid="{0894BC58-29DD-1A47-A7FA-3918C47C1800}" name="Columna4" dataDxfId="5"/>
     <tableColumn id="11" xr3:uid="{76AE19E7-5CA4-AC4C-9442-42356F884393}" name="Columna5"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Column4"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Column6"/>
@@ -1409,7 +1428,9 @@
   <dimension ref="A1:AB988"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="6" max="6" width="146.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="124.83203125" customWidth="1"/>
+    <col min="6" max="6" width="32.83203125" customWidth="1"/>
     <col min="7" max="8" width="32.1640625" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
   </cols>
@@ -1453,6 +1474,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1460,22 +1482,23 @@
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
@@ -1483,22 +1506,21 @@
         <v>4</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="H3" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J3" s="8"/>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1506,22 +1528,23 @@
         <v>4</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="H4" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" ht="39" customHeight="1">
+      <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -1529,22 +1552,23 @@
         <v>4</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="12" t="s">
         <v>11</v>
       </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="H5" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J5" s="8"/>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1552,22 +1576,23 @@
         <v>4</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A7" s="8"/>
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
@@ -1575,22 +1600,23 @@
         <v>13</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="H7" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A8" s="4"/>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
@@ -1598,22 +1624,23 @@
         <v>13</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A9" s="8"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1621,22 +1648,23 @@
         <v>13</v>
       </c>
       <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="H9" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A10" s="4"/>
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1644,22 +1672,23 @@
         <v>13</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A11" s="8"/>
       <c r="B11" s="5" t="s">
         <v>3</v>
       </c>
@@ -1667,22 +1696,23 @@
         <v>13</v>
       </c>
       <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="H11" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A12" s="4"/>
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1690,22 +1720,23 @@
         <v>13</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A13" s="8"/>
       <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
@@ -1713,22 +1744,23 @@
         <v>13</v>
       </c>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6" t="s">
+      <c r="E13" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="H13" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A14" s="4"/>
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1736,22 +1768,23 @@
         <v>13</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" ht="14">
+      <c r="A15" s="8"/>
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1759,22 +1792,23 @@
         <v>13</v>
       </c>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6" t="s">
+      <c r="E15" s="6" t="s">
         <v>24</v>
       </c>
+      <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
+      <c r="H15" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
     <row r="16" spans="1:12" ht="14">
+      <c r="A16" s="4"/>
       <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
@@ -1782,22 +1816,23 @@
         <v>13</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="2:12" ht="14">
+    <row r="17" spans="1:12" ht="14">
+      <c r="A17" s="8"/>
       <c r="B17" s="5" t="s">
         <v>3</v>
       </c>
@@ -1805,22 +1840,23 @@
         <v>13</v>
       </c>
       <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>26</v>
       </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
+      <c r="H17" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I17" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" spans="2:12" ht="14">
+    <row r="18" spans="1:12" ht="14">
+      <c r="A18" s="4"/>
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
@@ -1828,22 +1864,23 @@
         <v>13</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="2:12" ht="14">
+    <row r="19" spans="1:12" ht="14">
+      <c r="A19" s="8"/>
       <c r="B19" s="5" t="s">
         <v>3</v>
       </c>
@@ -1851,22 +1888,23 @@
         <v>13</v>
       </c>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>28</v>
       </c>
+      <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="H19" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="2:12" ht="14">
+    <row r="20" spans="1:12" ht="14">
+      <c r="A20" s="4"/>
       <c r="B20" s="1" t="s">
         <v>8</v>
       </c>
@@ -1874,22 +1912,23 @@
         <v>13</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="H20" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="2:12" ht="14">
+    <row r="21" spans="1:12" ht="14">
+      <c r="A21" s="8"/>
       <c r="B21" s="5" t="s">
         <v>20</v>
       </c>
@@ -1897,22 +1936,23 @@
         <v>13</v>
       </c>
       <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6" t="s">
+      <c r="E21" s="6" t="s">
         <v>30</v>
       </c>
+      <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
+      <c r="H21" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I21" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
-    <row r="22" spans="2:12" ht="14">
+    <row r="22" spans="1:12" ht="14">
+      <c r="A22" s="4"/>
       <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1920,22 +1960,23 @@
         <v>13</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="H22" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="2:12" ht="14">
+    <row r="23" spans="1:12" ht="14">
+      <c r="A23" s="8"/>
       <c r="B23" s="5" t="s">
         <v>20</v>
       </c>
@@ -1943,22 +1984,23 @@
         <v>13</v>
       </c>
       <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>32</v>
       </c>
+      <c r="F23" s="6"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+      <c r="H23" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
-    <row r="24" spans="2:12" ht="14">
+    <row r="24" spans="1:12" ht="14">
+      <c r="A24" s="4"/>
       <c r="B24" s="1" t="s">
         <v>20</v>
       </c>
@@ -1966,22 +2008,23 @@
         <v>13</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="H24" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="2:12" ht="14">
+    <row r="25" spans="1:12" ht="14">
+      <c r="A25" s="8"/>
       <c r="B25" s="5" t="s">
         <v>20</v>
       </c>
@@ -1989,22 +2032,23 @@
         <v>13</v>
       </c>
       <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>34</v>
       </c>
+      <c r="F25" s="6"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+      <c r="H25" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I25" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J25" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
-    <row r="26" spans="2:12" ht="14">
+    <row r="26" spans="1:12" ht="14">
+      <c r="A26" s="4"/>
       <c r="B26" s="1" t="s">
         <v>20</v>
       </c>
@@ -2012,22 +2056,23 @@
         <v>13</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="H26" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="2:12" ht="14">
+    <row r="27" spans="1:12" ht="14">
+      <c r="A27" s="8"/>
       <c r="B27" s="5" t="s">
         <v>20</v>
       </c>
@@ -2035,22 +2080,23 @@
         <v>13</v>
       </c>
       <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>36</v>
       </c>
+      <c r="F27" s="6"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
+      <c r="H27" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I27" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J27" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
     </row>
-    <row r="28" spans="2:12" ht="14">
+    <row r="28" spans="1:12" ht="14">
+      <c r="A28" s="4"/>
       <c r="B28" s="1" t="s">
         <v>20</v>
       </c>
@@ -2058,22 +2104,23 @@
         <v>13</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="H28" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="2:12" ht="14">
+    <row r="29" spans="1:12" ht="14">
+      <c r="A29" s="8"/>
       <c r="B29" s="5" t="s">
         <v>20</v>
       </c>
@@ -2081,22 +2128,23 @@
         <v>13</v>
       </c>
       <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
+      <c r="H29" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I29" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J29" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
-    <row r="30" spans="2:12" ht="14">
+    <row r="30" spans="1:12" ht="14">
+      <c r="A30" s="4"/>
       <c r="B30" s="1" t="s">
         <v>20</v>
       </c>
@@ -2104,22 +2152,23 @@
         <v>13</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+      <c r="H30" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="2:12" ht="14">
+    <row r="31" spans="1:12" ht="14">
+      <c r="A31" s="8"/>
       <c r="B31" s="5" t="s">
         <v>20</v>
       </c>
@@ -2127,22 +2176,23 @@
         <v>13</v>
       </c>
       <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>40</v>
       </c>
+      <c r="F31" s="6"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
+      <c r="H31" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I31" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
     </row>
-    <row r="32" spans="2:12" ht="14">
+    <row r="32" spans="1:12" ht="14">
+      <c r="A32" s="4"/>
       <c r="B32" s="1" t="s">
         <v>20</v>
       </c>
@@ -2150,22 +2200,23 @@
         <v>13</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
+      <c r="H32" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
     </row>
-    <row r="33" spans="2:12" ht="14">
+    <row r="33" spans="1:12" ht="14">
+      <c r="A33" s="8"/>
       <c r="B33" s="5" t="s">
         <v>20</v>
       </c>
@@ -2173,22 +2224,23 @@
         <v>13</v>
       </c>
       <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
+      <c r="H33" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J33" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="2:12" ht="14">
+    <row r="34" spans="1:12" ht="14">
+      <c r="A34" s="4"/>
       <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
@@ -2196,22 +2248,23 @@
         <v>13</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
+      <c r="H34" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
     </row>
-    <row r="35" spans="2:12" ht="14">
+    <row r="35" spans="1:12" ht="14">
+      <c r="A35" s="8"/>
       <c r="B35" s="5" t="s">
         <v>20</v>
       </c>
@@ -2219,22 +2272,23 @@
         <v>13</v>
       </c>
       <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6" t="s">
+      <c r="E35" s="6" t="s">
         <v>44</v>
       </c>
+      <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
+      <c r="H35" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="2:12" ht="14">
+    <row r="36" spans="1:12" ht="14">
+      <c r="A36" s="4"/>
       <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
@@ -2242,22 +2296,23 @@
         <v>13</v>
       </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
+      <c r="H36" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
     </row>
-    <row r="37" spans="2:12" ht="14">
+    <row r="37" spans="1:12" ht="14">
+      <c r="A37" s="8"/>
       <c r="B37" s="5" t="s">
         <v>20</v>
       </c>
@@ -2265,22 +2320,23 @@
         <v>13</v>
       </c>
       <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6" t="s">
+      <c r="E37" s="6" t="s">
         <v>46</v>
       </c>
+      <c r="F37" s="6"/>
       <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
+      <c r="H37" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I37" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J37" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
     </row>
-    <row r="38" spans="2:12" ht="14">
+    <row r="38" spans="1:12" ht="14">
+      <c r="A38" s="4"/>
       <c r="B38" s="1" t="s">
         <v>20</v>
       </c>
@@ -2288,22 +2344,23 @@
         <v>13</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
+      <c r="H38" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
     </row>
-    <row r="39" spans="2:12" ht="14">
+    <row r="39" spans="1:12" ht="14">
+      <c r="A39" s="8"/>
       <c r="B39" s="5" t="s">
         <v>20</v>
       </c>
@@ -2311,22 +2368,23 @@
         <v>13</v>
       </c>
       <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6" t="s">
+      <c r="E39" s="6" t="s">
         <v>48</v>
       </c>
+      <c r="F39" s="6"/>
       <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
+      <c r="H39" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I39" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J39" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="2:12" ht="14">
+    <row r="40" spans="1:12" ht="14">
+      <c r="A40" s="4"/>
       <c r="B40" s="1" t="s">
         <v>3</v>
       </c>
@@ -2334,22 +2392,23 @@
         <v>49</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
+      <c r="H40" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
     </row>
-    <row r="41" spans="2:12" ht="14">
+    <row r="41" spans="1:12" ht="14">
+      <c r="A41" s="8"/>
       <c r="B41" s="5" t="s">
         <v>3</v>
       </c>
@@ -2357,22 +2416,23 @@
         <v>51</v>
       </c>
       <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6" t="s">
+      <c r="E41" s="6" t="s">
         <v>52</v>
       </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
+      <c r="H41" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I41" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J41" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
     </row>
-    <row r="42" spans="2:12" ht="14">
+    <row r="42" spans="1:12" ht="14">
+      <c r="A42" s="4"/>
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
@@ -2380,22 +2440,23 @@
         <v>51</v>
       </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
+      <c r="H42" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
     </row>
-    <row r="43" spans="2:12" ht="14">
+    <row r="43" spans="1:12" ht="14">
+      <c r="A43" s="8"/>
       <c r="B43" s="5" t="s">
         <v>3</v>
       </c>
@@ -2403,22 +2464,23 @@
         <v>51</v>
       </c>
       <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6" t="s">
+      <c r="E43" s="6" t="s">
         <v>54</v>
       </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
+      <c r="H43" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I43" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J43" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J43" s="8"/>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
     </row>
-    <row r="44" spans="2:12" ht="14">
+    <row r="44" spans="1:12" ht="14">
+      <c r="A44" s="4"/>
       <c r="B44" s="1" t="s">
         <v>3</v>
       </c>
@@ -2426,22 +2488,23 @@
         <v>51</v>
       </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
+      <c r="H44" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
     </row>
-    <row r="45" spans="2:12" ht="14">
+    <row r="45" spans="1:12" ht="14">
+      <c r="A45" s="8"/>
       <c r="B45" s="5" t="s">
         <v>3</v>
       </c>
@@ -2449,22 +2512,23 @@
         <v>51</v>
       </c>
       <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6" t="s">
+      <c r="E45" s="6" t="s">
         <v>56</v>
       </c>
+      <c r="F45" s="6"/>
       <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
+      <c r="H45" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I45" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J45" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J45" s="8"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="2:12" ht="14">
+    <row r="46" spans="1:12" ht="14">
+      <c r="A46" s="4"/>
       <c r="B46" s="1" t="s">
         <v>3</v>
       </c>
@@ -2472,22 +2536,23 @@
         <v>51</v>
       </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="H46" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
     </row>
-    <row r="47" spans="2:12" ht="14">
+    <row r="47" spans="1:12" ht="14">
+      <c r="A47" s="8"/>
       <c r="B47" s="5" t="s">
         <v>3</v>
       </c>
@@ -2495,22 +2560,23 @@
         <v>51</v>
       </c>
       <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6" t="s">
+      <c r="E47" s="6" t="s">
         <v>58</v>
       </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
+      <c r="H47" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I47" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J47" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J47" s="8"/>
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
-    <row r="48" spans="2:12" ht="14">
+    <row r="48" spans="1:12" ht="14">
+      <c r="A48" s="4"/>
       <c r="B48" s="1" t="s">
         <v>3</v>
       </c>
@@ -2518,22 +2584,23 @@
         <v>51</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
+      <c r="H48" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
     </row>
-    <row r="49" spans="2:12" ht="14">
+    <row r="49" spans="1:12" ht="14">
+      <c r="A49" s="8"/>
       <c r="B49" s="5" t="s">
         <v>3</v>
       </c>
@@ -2541,22 +2608,23 @@
         <v>51</v>
       </c>
       <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6" t="s">
+      <c r="E49" s="6" t="s">
         <v>60</v>
       </c>
+      <c r="F49" s="6"/>
       <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
+      <c r="H49" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I49" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J49" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J49" s="8"/>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
     </row>
-    <row r="50" spans="2:12" ht="14">
+    <row r="50" spans="1:12" ht="14">
+      <c r="A50" s="4"/>
       <c r="B50" s="1" t="s">
         <v>3</v>
       </c>
@@ -2564,22 +2632,23 @@
         <v>61</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
+      <c r="H50" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J50" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
     </row>
-    <row r="51" spans="2:12" ht="14">
+    <row r="51" spans="1:12" ht="14">
+      <c r="A51" s="8"/>
       <c r="B51" s="5" t="s">
         <v>3</v>
       </c>
@@ -2587,22 +2656,23 @@
         <v>61</v>
       </c>
       <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6" t="s">
+      <c r="E51" s="6" t="s">
         <v>63</v>
       </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
+      <c r="H51" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I51" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J51" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J51" s="8"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
     </row>
-    <row r="52" spans="2:12" ht="14">
+    <row r="52" spans="1:12" ht="14">
+      <c r="A52" s="4"/>
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
@@ -2610,22 +2680,23 @@
         <v>61</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
+      <c r="H52" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
     </row>
-    <row r="53" spans="2:12" ht="14">
+    <row r="53" spans="1:12" ht="14">
+      <c r="A53" s="8"/>
       <c r="B53" s="5" t="s">
         <v>3</v>
       </c>
@@ -2633,22 +2704,23 @@
         <v>65</v>
       </c>
       <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6" t="s">
+      <c r="E53" s="6" t="s">
         <v>66</v>
       </c>
+      <c r="F53" s="6"/>
       <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
+      <c r="H53" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I53" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J53" s="8"/>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
     </row>
-    <row r="54" spans="2:12" ht="14">
+    <row r="54" spans="1:12" ht="14">
+      <c r="A54" s="4"/>
       <c r="B54" s="1" t="s">
         <v>3</v>
       </c>
@@ -2656,22 +2728,23 @@
         <v>65</v>
       </c>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
+      <c r="H54" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I54" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
     </row>
-    <row r="55" spans="2:12" ht="14">
+    <row r="55" spans="1:12" ht="14">
+      <c r="A55" s="8"/>
       <c r="B55" s="5" t="s">
         <v>3</v>
       </c>
@@ -2679,22 +2752,23 @@
         <v>65</v>
       </c>
       <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6" t="s">
+      <c r="E55" s="6" t="s">
         <v>68</v>
       </c>
+      <c r="F55" s="6"/>
       <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
+      <c r="H55" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I55" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J55" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J55" s="8"/>
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
     </row>
-    <row r="56" spans="2:12" ht="14">
+    <row r="56" spans="1:12" ht="14">
+      <c r="A56" s="4"/>
       <c r="B56" s="1" t="s">
         <v>3</v>
       </c>
@@ -2702,22 +2776,23 @@
         <v>65</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>69</v>
       </c>
+      <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
+      <c r="H56" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I56" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
     </row>
-    <row r="57" spans="2:12" ht="14">
+    <row r="57" spans="1:12" ht="14">
+      <c r="A57" s="8"/>
       <c r="B57" s="5" t="s">
         <v>3</v>
       </c>
@@ -2725,22 +2800,23 @@
         <v>65</v>
       </c>
       <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6" t="s">
+      <c r="E57" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="F57" s="6"/>
       <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
+      <c r="H57" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I57" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J57" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J57" s="8"/>
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
     </row>
-    <row r="58" spans="2:12" ht="14">
+    <row r="58" spans="1:12" ht="14">
+      <c r="A58" s="4"/>
       <c r="B58" s="1" t="s">
         <v>20</v>
       </c>
@@ -2748,22 +2824,23 @@
         <v>13</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>71</v>
       </c>
+      <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
+      <c r="H58" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I58" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
     </row>
-    <row r="59" spans="2:12" ht="14">
+    <row r="59" spans="1:12" ht="14">
+      <c r="A59" s="8"/>
       <c r="B59" s="5" t="s">
         <v>3</v>
       </c>
@@ -2771,22 +2848,23 @@
         <v>13</v>
       </c>
       <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6" t="s">
+      <c r="E59" s="6" t="s">
         <v>72</v>
       </c>
+      <c r="F59" s="6"/>
       <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
+      <c r="H59" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I59" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J59" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J59" s="8"/>
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
     </row>
-    <row r="60" spans="2:12" ht="14">
+    <row r="60" spans="1:12" ht="14">
+      <c r="A60" s="4"/>
       <c r="B60" s="1" t="s">
         <v>20</v>
       </c>
@@ -2794,22 +2872,23 @@
         <v>13</v>
       </c>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
+      <c r="H60" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I60" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
     </row>
-    <row r="61" spans="2:12" ht="14">
+    <row r="61" spans="1:12" ht="14">
+      <c r="A61" s="8"/>
       <c r="B61" s="5" t="s">
         <v>20</v>
       </c>
@@ -2817,22 +2896,23 @@
         <v>13</v>
       </c>
       <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6" t="s">
+      <c r="E61" s="6" t="s">
         <v>74</v>
       </c>
+      <c r="F61" s="6"/>
       <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
+      <c r="H61" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I61" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J61" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J61" s="8"/>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
     </row>
-    <row r="62" spans="2:12" ht="14">
+    <row r="62" spans="1:12" ht="14">
+      <c r="A62" s="4"/>
       <c r="B62" s="1" t="s">
         <v>3</v>
       </c>
@@ -2840,22 +2920,23 @@
         <v>13</v>
       </c>
       <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>75</v>
       </c>
+      <c r="F62" s="2"/>
       <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
+      <c r="H62" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I62" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
     </row>
-    <row r="63" spans="2:12" ht="14">
+    <row r="63" spans="1:12" ht="14">
+      <c r="A63" s="8"/>
       <c r="B63" s="5" t="s">
         <v>3</v>
       </c>
@@ -2863,22 +2944,23 @@
         <v>13</v>
       </c>
       <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6" t="s">
+      <c r="E63" s="6" t="s">
         <v>76</v>
       </c>
+      <c r="F63" s="6"/>
       <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
+      <c r="H63" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I63" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J63" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J63" s="8"/>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
     </row>
-    <row r="64" spans="2:12" ht="14">
+    <row r="64" spans="1:12" ht="14">
+      <c r="A64" s="4"/>
       <c r="B64" s="1" t="s">
         <v>3</v>
       </c>
@@ -2886,22 +2968,23 @@
         <v>13</v>
       </c>
       <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="F64" s="2"/>
       <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
+      <c r="H64" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I64" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
     </row>
-    <row r="65" spans="2:12" ht="14">
+    <row r="65" spans="1:12" ht="14">
+      <c r="A65" s="8"/>
       <c r="B65" s="5" t="s">
         <v>3</v>
       </c>
@@ -2909,22 +2992,23 @@
         <v>13</v>
       </c>
       <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6" t="s">
+      <c r="E65" s="6" t="s">
         <v>78</v>
       </c>
+      <c r="F65" s="6"/>
       <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
+      <c r="H65" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I65" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J65" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J65" s="8"/>
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
     </row>
-    <row r="66" spans="2:12" ht="14">
+    <row r="66" spans="1:12" ht="14">
+      <c r="A66" s="4"/>
       <c r="B66" s="1" t="s">
         <v>20</v>
       </c>
@@ -2932,22 +3016,23 @@
         <v>13</v>
       </c>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>79</v>
       </c>
+      <c r="F66" s="2"/>
       <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
+      <c r="H66" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I66" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
     </row>
-    <row r="67" spans="2:12" ht="14">
+    <row r="67" spans="1:12" ht="14">
+      <c r="A67" s="8"/>
       <c r="B67" s="5" t="s">
         <v>20</v>
       </c>
@@ -2955,22 +3040,23 @@
         <v>13</v>
       </c>
       <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6" t="s">
+      <c r="E67" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="F67" s="6"/>
       <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
+      <c r="H67" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I67" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J67" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J67" s="8"/>
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
     </row>
-    <row r="68" spans="2:12" ht="14">
+    <row r="68" spans="1:12" ht="14">
+      <c r="A68" s="4"/>
       <c r="B68" s="1" t="s">
         <v>20</v>
       </c>
@@ -2978,22 +3064,23 @@
         <v>13</v>
       </c>
       <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>81</v>
       </c>
+      <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
+      <c r="H68" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I68" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J68" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
     </row>
-    <row r="69" spans="2:12" ht="14">
+    <row r="69" spans="1:12" ht="14">
+      <c r="A69" s="8"/>
       <c r="B69" s="5" t="s">
         <v>20</v>
       </c>
@@ -3001,22 +3088,23 @@
         <v>13</v>
       </c>
       <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6" t="s">
+      <c r="E69" s="6" t="s">
         <v>82</v>
       </c>
+      <c r="F69" s="6"/>
       <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
+      <c r="H69" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I69" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J69" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J69" s="8"/>
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
     </row>
-    <row r="70" spans="2:12" ht="14">
+    <row r="70" spans="1:12" ht="14">
+      <c r="A70" s="4"/>
       <c r="B70" s="1" t="s">
         <v>20</v>
       </c>
@@ -3024,22 +3112,23 @@
         <v>13</v>
       </c>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="F70" s="2"/>
       <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
+      <c r="H70" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I70" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
     </row>
-    <row r="71" spans="2:12" ht="14">
+    <row r="71" spans="1:12" ht="14">
+      <c r="A71" s="8"/>
       <c r="B71" s="5" t="s">
         <v>3</v>
       </c>
@@ -3047,22 +3136,23 @@
         <v>13</v>
       </c>
       <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6" t="s">
+      <c r="E71" s="6" t="s">
         <v>84</v>
       </c>
+      <c r="F71" s="6"/>
       <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
+      <c r="H71" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I71" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J71" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J71" s="8"/>
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
     </row>
-    <row r="72" spans="2:12" ht="14">
+    <row r="72" spans="1:12" ht="14">
+      <c r="A72" s="4"/>
       <c r="B72" s="1" t="s">
         <v>20</v>
       </c>
@@ -3070,22 +3160,23 @@
         <v>13</v>
       </c>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="F72" s="2"/>
       <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
+      <c r="H72" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I72" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J72" s="4"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
     </row>
-    <row r="73" spans="2:12" ht="14">
+    <row r="73" spans="1:12" ht="14">
+      <c r="A73" s="8"/>
       <c r="B73" s="5" t="s">
         <v>20</v>
       </c>
@@ -3093,22 +3184,23 @@
         <v>13</v>
       </c>
       <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6" t="s">
+      <c r="E73" s="6" t="s">
         <v>86</v>
       </c>
+      <c r="F73" s="6"/>
       <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
+      <c r="H73" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I73" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J73" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J73" s="8"/>
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
     </row>
-    <row r="74" spans="2:12" ht="14">
+    <row r="74" spans="1:12" ht="14">
+      <c r="A74" s="4"/>
       <c r="B74" s="1" t="s">
         <v>3</v>
       </c>
@@ -3116,22 +3208,23 @@
         <v>13</v>
       </c>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="F74" s="2"/>
       <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
+      <c r="H74" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I74" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J74" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
     </row>
-    <row r="75" spans="2:12" ht="14">
+    <row r="75" spans="1:12" ht="14">
+      <c r="A75" s="8"/>
       <c r="B75" s="5" t="s">
         <v>3</v>
       </c>
@@ -3139,22 +3232,23 @@
         <v>13</v>
       </c>
       <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6" t="s">
+      <c r="E75" s="6" t="s">
         <v>88</v>
       </c>
+      <c r="F75" s="6"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
+      <c r="H75" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I75" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J75" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J75" s="8"/>
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
     </row>
-    <row r="76" spans="2:12" ht="14">
+    <row r="76" spans="1:12" ht="14">
+      <c r="A76" s="4"/>
       <c r="B76" s="1" t="s">
         <v>3</v>
       </c>
@@ -3162,22 +3256,23 @@
         <v>13</v>
       </c>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>89</v>
       </c>
+      <c r="F76" s="2"/>
       <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
+      <c r="H76" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I76" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J76" s="4"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
     </row>
-    <row r="77" spans="2:12" ht="14">
+    <row r="77" spans="1:12" ht="14">
+      <c r="A77" s="8"/>
       <c r="B77" s="5" t="s">
         <v>3</v>
       </c>
@@ -3185,22 +3280,23 @@
         <v>13</v>
       </c>
       <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6" t="s">
+      <c r="E77" s="6" t="s">
         <v>90</v>
       </c>
+      <c r="F77" s="6"/>
       <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
+      <c r="H77" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I77" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J77" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J77" s="8"/>
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
     </row>
-    <row r="78" spans="2:12" ht="14">
+    <row r="78" spans="1:12" ht="14">
+      <c r="A78" s="4"/>
       <c r="B78" s="1" t="s">
         <v>3</v>
       </c>
@@ -3208,22 +3304,23 @@
         <v>13</v>
       </c>
       <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>91</v>
       </c>
+      <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
+      <c r="H78" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I78" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J78" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
     </row>
-    <row r="79" spans="2:12" ht="14">
+    <row r="79" spans="1:12" ht="14">
+      <c r="A79" s="8"/>
       <c r="B79" s="5" t="s">
         <v>20</v>
       </c>
@@ -3231,22 +3328,23 @@
         <v>13</v>
       </c>
       <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6" t="s">
+      <c r="E79" s="6" t="s">
         <v>92</v>
       </c>
+      <c r="F79" s="6"/>
       <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
+      <c r="H79" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I79" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J79" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J79" s="8"/>
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
     </row>
-    <row r="80" spans="2:12" ht="14">
+    <row r="80" spans="1:12" ht="14">
+      <c r="A80" s="4"/>
       <c r="B80" s="1" t="s">
         <v>20</v>
       </c>
@@ -3254,22 +3352,23 @@
         <v>13</v>
       </c>
       <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>93</v>
       </c>
+      <c r="F80" s="2"/>
       <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
+      <c r="H80" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I80" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J80" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
     </row>
-    <row r="81" spans="2:12" ht="14">
+    <row r="81" spans="1:12" ht="14">
+      <c r="A81" s="8"/>
       <c r="B81" s="5" t="s">
         <v>20</v>
       </c>
@@ -3277,22 +3376,23 @@
         <v>13</v>
       </c>
       <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6" t="s">
+      <c r="E81" s="6" t="s">
         <v>94</v>
       </c>
+      <c r="F81" s="6"/>
       <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
+      <c r="H81" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I81" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J81" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J81" s="8"/>
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
     </row>
-    <row r="82" spans="2:12" ht="14">
+    <row r="82" spans="1:12" ht="14">
+      <c r="A82" s="4"/>
       <c r="B82" s="1" t="s">
         <v>20</v>
       </c>
@@ -3300,22 +3400,23 @@
         <v>13</v>
       </c>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="F82" s="2"/>
       <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
+      <c r="H82" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I82" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J82" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J82" s="4"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
     </row>
-    <row r="83" spans="2:12" ht="14">
+    <row r="83" spans="1:12" ht="14">
+      <c r="A83" s="8"/>
       <c r="B83" s="5" t="s">
         <v>20</v>
       </c>
@@ -3323,22 +3424,23 @@
         <v>13</v>
       </c>
       <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6" t="s">
+      <c r="E83" s="6" t="s">
         <v>96</v>
       </c>
+      <c r="F83" s="6"/>
       <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
+      <c r="H83" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I83" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J83" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J83" s="8"/>
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
     </row>
-    <row r="84" spans="2:12" ht="14">
+    <row r="84" spans="1:12" ht="14">
+      <c r="A84" s="4"/>
       <c r="B84" s="1" t="s">
         <v>20</v>
       </c>
@@ -3346,22 +3448,23 @@
         <v>13</v>
       </c>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2" t="s">
+      <c r="E84" s="2" t="s">
         <v>97</v>
       </c>
+      <c r="F84" s="2"/>
       <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
+      <c r="H84" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I84" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J84" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
     </row>
-    <row r="85" spans="2:12" ht="14">
+    <row r="85" spans="1:12" ht="14">
+      <c r="A85" s="8"/>
       <c r="B85" s="5" t="s">
         <v>20</v>
       </c>
@@ -3369,22 +3472,23 @@
         <v>13</v>
       </c>
       <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6" t="s">
+      <c r="E85" s="6" t="s">
         <v>98</v>
       </c>
+      <c r="F85" s="6"/>
       <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
+      <c r="H85" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I85" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J85" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J85" s="8"/>
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
     </row>
-    <row r="86" spans="2:12" ht="14">
+    <row r="86" spans="1:12" ht="14">
+      <c r="A86" s="4"/>
       <c r="B86" s="1" t="s">
         <v>20</v>
       </c>
@@ -3392,22 +3496,23 @@
         <v>13</v>
       </c>
       <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2" t="s">
+      <c r="E86" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="F86" s="2"/>
       <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
+      <c r="H86" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I86" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J86" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
     </row>
-    <row r="87" spans="2:12" ht="14">
+    <row r="87" spans="1:12" ht="14">
+      <c r="A87" s="8"/>
       <c r="B87" s="5" t="s">
         <v>20</v>
       </c>
@@ -3415,22 +3520,23 @@
         <v>13</v>
       </c>
       <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6" t="s">
+      <c r="E87" s="6" t="s">
         <v>100</v>
       </c>
+      <c r="F87" s="6"/>
       <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
+      <c r="H87" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I87" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J87" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J87" s="8"/>
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
     </row>
-    <row r="88" spans="2:12" ht="14">
+    <row r="88" spans="1:12" ht="14">
+      <c r="A88" s="4"/>
       <c r="B88" s="1" t="s">
         <v>20</v>
       </c>
@@ -3438,22 +3544,23 @@
         <v>13</v>
       </c>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>101</v>
       </c>
+      <c r="F88" s="2"/>
       <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
+      <c r="H88" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I88" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J88" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
     </row>
-    <row r="89" spans="2:12" ht="14">
+    <row r="89" spans="1:12" ht="14">
+      <c r="A89" s="8"/>
       <c r="B89" s="5" t="s">
         <v>3</v>
       </c>
@@ -3461,22 +3568,23 @@
         <v>13</v>
       </c>
       <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6" t="s">
+      <c r="E89" s="6" t="s">
         <v>102</v>
       </c>
+      <c r="F89" s="6"/>
       <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
+      <c r="H89" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I89" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J89" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J89" s="8"/>
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
     </row>
-    <row r="90" spans="2:12" ht="14">
+    <row r="90" spans="1:12" ht="14">
+      <c r="A90" s="4"/>
       <c r="B90" s="1" t="s">
         <v>3</v>
       </c>
@@ -3484,22 +3592,23 @@
         <v>13</v>
       </c>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2" t="s">
+      <c r="E90" s="2" t="s">
         <v>103</v>
       </c>
+      <c r="F90" s="2"/>
       <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
+      <c r="H90" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I90" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J90" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J90" s="4"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
     </row>
-    <row r="91" spans="2:12" ht="14">
+    <row r="91" spans="1:12" ht="14">
+      <c r="A91" s="8"/>
       <c r="B91" s="5" t="s">
         <v>20</v>
       </c>
@@ -3507,22 +3616,23 @@
         <v>13</v>
       </c>
       <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6" t="s">
+      <c r="E91" s="6" t="s">
         <v>104</v>
       </c>
+      <c r="F91" s="6"/>
       <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
+      <c r="H91" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I91" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J91" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J91" s="8"/>
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
     </row>
-    <row r="92" spans="2:12" ht="14">
+    <row r="92" spans="1:12" ht="14">
+      <c r="A92" s="4"/>
       <c r="B92" s="1" t="s">
         <v>20</v>
       </c>
@@ -3530,22 +3640,23 @@
         <v>13</v>
       </c>
       <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2" t="s">
+      <c r="E92" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="F92" s="2"/>
       <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
+      <c r="H92" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I92" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J92" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J92" s="4"/>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
     </row>
-    <row r="93" spans="2:12" ht="14">
+    <row r="93" spans="1:12" ht="14">
+      <c r="A93" s="8"/>
       <c r="B93" s="5" t="s">
         <v>20</v>
       </c>
@@ -3553,22 +3664,23 @@
         <v>13</v>
       </c>
       <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6" t="s">
+      <c r="E93" s="6" t="s">
         <v>106</v>
       </c>
+      <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
+      <c r="H93" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I93" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J93" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J93" s="8"/>
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
     </row>
-    <row r="94" spans="2:12" ht="14">
+    <row r="94" spans="1:12" ht="14">
+      <c r="A94" s="4"/>
       <c r="B94" s="1" t="s">
         <v>20</v>
       </c>
@@ -3576,22 +3688,23 @@
         <v>13</v>
       </c>
       <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2" t="s">
+      <c r="E94" s="2" t="s">
         <v>107</v>
       </c>
+      <c r="F94" s="2"/>
       <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
+      <c r="H94" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I94" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J94" s="4"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
     </row>
-    <row r="95" spans="2:12" ht="14">
+    <row r="95" spans="1:12" ht="14">
+      <c r="A95" s="8"/>
       <c r="B95" s="5" t="s">
         <v>20</v>
       </c>
@@ -3599,22 +3712,23 @@
         <v>13</v>
       </c>
       <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6" t="s">
+      <c r="E95" s="6" t="s">
         <v>108</v>
       </c>
+      <c r="F95" s="6"/>
       <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
+      <c r="H95" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I95" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J95" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J95" s="8"/>
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
     </row>
-    <row r="96" spans="2:12" ht="14">
+    <row r="96" spans="1:12" ht="14">
+      <c r="A96" s="4"/>
       <c r="B96" s="1" t="s">
         <v>20</v>
       </c>
@@ -3622,22 +3736,23 @@
         <v>13</v>
       </c>
       <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>109</v>
       </c>
+      <c r="F96" s="2"/>
       <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
+      <c r="H96" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I96" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
     </row>
-    <row r="97" spans="2:12" ht="14">
+    <row r="97" spans="1:12" ht="14">
+      <c r="A97" s="8"/>
       <c r="B97" s="5" t="s">
         <v>20</v>
       </c>
@@ -3645,22 +3760,23 @@
         <v>13</v>
       </c>
       <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6" t="s">
+      <c r="E97" s="6" t="s">
         <v>110</v>
       </c>
+      <c r="F97" s="6"/>
       <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
+      <c r="H97" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I97" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J97" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J97" s="8"/>
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
     </row>
-    <row r="98" spans="2:12" ht="14">
+    <row r="98" spans="1:12" ht="14">
+      <c r="A98" s="4"/>
       <c r="B98" s="1" t="s">
         <v>3</v>
       </c>
@@ -3668,22 +3784,23 @@
         <v>13</v>
       </c>
       <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2" t="s">
+      <c r="E98" s="2" t="s">
         <v>111</v>
       </c>
+      <c r="F98" s="2"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
+      <c r="H98" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I98" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J98" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J98" s="4"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
     </row>
-    <row r="99" spans="2:12" ht="14">
+    <row r="99" spans="1:12" ht="14">
+      <c r="A99" s="8"/>
       <c r="B99" s="5" t="s">
         <v>3</v>
       </c>
@@ -3691,22 +3808,23 @@
         <v>13</v>
       </c>
       <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6" t="s">
+      <c r="E99" s="6" t="s">
         <v>112</v>
       </c>
+      <c r="F99" s="6"/>
       <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
+      <c r="H99" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I99" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J99" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J99" s="8"/>
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
     </row>
-    <row r="100" spans="2:12" ht="14">
+    <row r="100" spans="1:12" ht="14">
+      <c r="A100" s="4"/>
       <c r="B100" s="1" t="s">
         <v>3</v>
       </c>
@@ -3714,22 +3832,23 @@
         <v>13</v>
       </c>
       <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2" t="s">
+      <c r="E100" s="2" t="s">
         <v>113</v>
       </c>
+      <c r="F100" s="2"/>
       <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
+      <c r="H100" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I100" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
     </row>
-    <row r="101" spans="2:12" ht="14">
+    <row r="101" spans="1:12" ht="14">
+      <c r="A101" s="8"/>
       <c r="B101" s="5" t="s">
         <v>3</v>
       </c>
@@ -3737,22 +3856,23 @@
         <v>13</v>
       </c>
       <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6" t="s">
+      <c r="E101" s="6" t="s">
         <v>114</v>
       </c>
+      <c r="F101" s="6"/>
       <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
+      <c r="H101" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I101" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J101" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J101" s="8"/>
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
     </row>
-    <row r="102" spans="2:12" ht="14">
+    <row r="102" spans="1:12" ht="14">
+      <c r="A102" s="4"/>
       <c r="B102" s="1" t="s">
         <v>20</v>
       </c>
@@ -3760,22 +3880,23 @@
         <v>13</v>
       </c>
       <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2" t="s">
+      <c r="E102" s="2" t="s">
         <v>115</v>
       </c>
+      <c r="F102" s="2"/>
       <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
+      <c r="H102" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I102" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J102" s="4"/>
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
     </row>
-    <row r="103" spans="2:12" ht="14">
+    <row r="103" spans="1:12" ht="14">
+      <c r="A103" s="8"/>
       <c r="B103" s="5" t="s">
         <v>20</v>
       </c>
@@ -3783,22 +3904,23 @@
         <v>13</v>
       </c>
       <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6" t="s">
+      <c r="E103" s="6" t="s">
         <v>116</v>
       </c>
+      <c r="F103" s="6"/>
       <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
+      <c r="H103" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I103" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J103" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J103" s="8"/>
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
     </row>
-    <row r="104" spans="2:12" ht="14">
+    <row r="104" spans="1:12" ht="14">
+      <c r="A104" s="4"/>
       <c r="B104" s="1" t="s">
         <v>20</v>
       </c>
@@ -3806,22 +3928,23 @@
         <v>13</v>
       </c>
       <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="F104" s="2"/>
       <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
+      <c r="H104" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I104" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J104" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
     </row>
-    <row r="105" spans="2:12" ht="14">
+    <row r="105" spans="1:12" ht="14">
+      <c r="A105" s="8"/>
       <c r="B105" s="5" t="s">
         <v>20</v>
       </c>
@@ -3829,22 +3952,23 @@
         <v>13</v>
       </c>
       <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6" t="s">
+      <c r="E105" s="6" t="s">
         <v>118</v>
       </c>
+      <c r="F105" s="6"/>
       <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
+      <c r="H105" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I105" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J105" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J105" s="8"/>
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
     </row>
-    <row r="106" spans="2:12" ht="14">
+    <row r="106" spans="1:12" ht="14">
+      <c r="A106" s="4"/>
       <c r="B106" s="1" t="s">
         <v>20</v>
       </c>
@@ -3852,22 +3976,23 @@
         <v>13</v>
       </c>
       <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2" t="s">
+      <c r="E106" s="2" t="s">
         <v>119</v>
       </c>
+      <c r="F106" s="2"/>
       <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
+      <c r="H106" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I106" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J106" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J106" s="4"/>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
     </row>
-    <row r="107" spans="2:12" ht="14">
+    <row r="107" spans="1:12" ht="14">
+      <c r="A107" s="8"/>
       <c r="B107" s="5" t="s">
         <v>20</v>
       </c>
@@ -3875,22 +4000,23 @@
         <v>13</v>
       </c>
       <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6" t="s">
+      <c r="E107" s="6" t="s">
         <v>120</v>
       </c>
+      <c r="F107" s="6"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
+      <c r="H107" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I107" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J107" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J107" s="8"/>
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
     </row>
-    <row r="108" spans="2:12" ht="14">
+    <row r="108" spans="1:12" ht="14">
+      <c r="A108" s="4"/>
       <c r="B108" s="1" t="s">
         <v>20</v>
       </c>
@@ -3898,22 +4024,23 @@
         <v>13</v>
       </c>
       <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2" t="s">
+      <c r="E108" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="F108" s="2"/>
       <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
+      <c r="H108" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I108" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J108" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J108" s="4"/>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
     </row>
-    <row r="109" spans="2:12" ht="14">
+    <row r="109" spans="1:12" ht="14">
+      <c r="A109" s="8"/>
       <c r="B109" s="5" t="s">
         <v>20</v>
       </c>
@@ -3921,22 +4048,23 @@
         <v>13</v>
       </c>
       <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6" t="s">
+      <c r="E109" s="6" t="s">
         <v>122</v>
       </c>
+      <c r="F109" s="6"/>
       <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
+      <c r="H109" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I109" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J109" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J109" s="8"/>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
-    <row r="110" spans="2:12" ht="14">
+    <row r="110" spans="1:12" ht="14">
+      <c r="A110" s="4"/>
       <c r="B110" s="1" t="s">
         <v>20</v>
       </c>
@@ -3944,22 +4072,23 @@
         <v>13</v>
       </c>
       <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2" t="s">
+      <c r="E110" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="F110" s="2"/>
       <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
+      <c r="H110" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I110" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J110" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
     </row>
-    <row r="111" spans="2:12" ht="14">
+    <row r="111" spans="1:12" ht="14">
+      <c r="A111" s="8"/>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
@@ -3967,22 +4096,23 @@
         <v>13</v>
       </c>
       <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6" t="s">
+      <c r="E111" s="6" t="s">
         <v>124</v>
       </c>
+      <c r="F111" s="6"/>
       <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
+      <c r="H111" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I111" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J111" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J111" s="8"/>
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
     </row>
-    <row r="112" spans="2:12" ht="14">
+    <row r="112" spans="1:12" ht="14">
+      <c r="A112" s="4"/>
       <c r="B112" s="1" t="s">
         <v>3</v>
       </c>
@@ -3990,22 +4120,23 @@
         <v>13</v>
       </c>
       <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2" t="s">
+      <c r="E112" s="2" t="s">
         <v>125</v>
       </c>
+      <c r="F112" s="2"/>
       <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
+      <c r="H112" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I112" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J112" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
     </row>
-    <row r="113" spans="2:12" ht="14">
+    <row r="113" spans="1:12" ht="14">
+      <c r="A113" s="8"/>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
@@ -4013,22 +4144,23 @@
         <v>13</v>
       </c>
       <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6" t="s">
+      <c r="E113" s="6" t="s">
         <v>126</v>
       </c>
+      <c r="F113" s="6"/>
       <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
+      <c r="H113" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I113" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J113" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J113" s="8"/>
       <c r="K113" s="8"/>
       <c r="L113" s="8"/>
     </row>
-    <row r="114" spans="2:12" ht="14">
+    <row r="114" spans="1:12" ht="14">
+      <c r="A114" s="4"/>
       <c r="B114" s="1" t="s">
         <v>3</v>
       </c>
@@ -4036,22 +4168,23 @@
         <v>13</v>
       </c>
       <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>127</v>
       </c>
+      <c r="F114" s="2"/>
       <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
+      <c r="H114" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I114" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J114" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
     </row>
-    <row r="115" spans="2:12" ht="14">
+    <row r="115" spans="1:12" ht="14">
+      <c r="A115" s="8"/>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
@@ -4059,22 +4192,23 @@
         <v>13</v>
       </c>
       <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6" t="s">
+      <c r="E115" s="6" t="s">
         <v>128</v>
       </c>
+      <c r="F115" s="6"/>
       <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
+      <c r="H115" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I115" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J115" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J115" s="8"/>
       <c r="K115" s="8"/>
       <c r="L115" s="8"/>
     </row>
-    <row r="116" spans="2:12" ht="14">
+    <row r="116" spans="1:12" ht="14">
+      <c r="A116" s="4"/>
       <c r="B116" s="1" t="s">
         <v>3</v>
       </c>
@@ -4082,22 +4216,23 @@
         <v>13</v>
       </c>
       <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2" t="s">
+      <c r="E116" s="2" t="s">
         <v>129</v>
       </c>
+      <c r="F116" s="2"/>
       <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
+      <c r="H116" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I116" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J116" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
     </row>
-    <row r="117" spans="2:12" ht="14">
+    <row r="117" spans="1:12" ht="14">
+      <c r="A117" s="8"/>
       <c r="B117" s="5" t="s">
         <v>20</v>
       </c>
@@ -4105,22 +4240,23 @@
         <v>13</v>
       </c>
       <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6" t="s">
+      <c r="E117" s="6" t="s">
         <v>130</v>
       </c>
+      <c r="F117" s="6"/>
       <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
+      <c r="H117" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I117" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J117" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J117" s="8"/>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
     </row>
-    <row r="118" spans="2:12" ht="14">
+    <row r="118" spans="1:12" ht="14">
+      <c r="A118" s="4"/>
       <c r="B118" s="1" t="s">
         <v>20</v>
       </c>
@@ -4128,22 +4264,23 @@
         <v>13</v>
       </c>
       <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2" t="s">
+      <c r="E118" s="2" t="s">
         <v>131</v>
       </c>
+      <c r="F118" s="2"/>
       <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
+      <c r="H118" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I118" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J118" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
     </row>
-    <row r="119" spans="2:12" ht="14">
+    <row r="119" spans="1:12" ht="14">
+      <c r="A119" s="8"/>
       <c r="B119" s="5" t="s">
         <v>20</v>
       </c>
@@ -4151,22 +4288,23 @@
         <v>13</v>
       </c>
       <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6" t="s">
+      <c r="E119" s="6" t="s">
         <v>132</v>
       </c>
+      <c r="F119" s="6"/>
       <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
+      <c r="H119" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I119" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J119" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J119" s="8"/>
       <c r="K119" s="8"/>
       <c r="L119" s="8"/>
     </row>
-    <row r="120" spans="2:12" ht="14">
+    <row r="120" spans="1:12" ht="14">
+      <c r="A120" s="4"/>
       <c r="B120" s="1" t="s">
         <v>20</v>
       </c>
@@ -4174,22 +4312,23 @@
         <v>13</v>
       </c>
       <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2" t="s">
+      <c r="E120" s="2" t="s">
         <v>133</v>
       </c>
+      <c r="F120" s="2"/>
       <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
+      <c r="H120" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I120" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J120" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
     </row>
-    <row r="121" spans="2:12" ht="14">
+    <row r="121" spans="1:12" ht="14">
+      <c r="A121" s="8"/>
       <c r="B121" s="5" t="s">
         <v>20</v>
       </c>
@@ -4197,22 +4336,23 @@
         <v>13</v>
       </c>
       <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6" t="s">
+      <c r="E121" s="6" t="s">
         <v>134</v>
       </c>
+      <c r="F121" s="6"/>
       <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
+      <c r="H121" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I121" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J121" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J121" s="8"/>
       <c r="K121" s="8"/>
       <c r="L121" s="8"/>
     </row>
-    <row r="122" spans="2:12" ht="14">
+    <row r="122" spans="1:12" ht="14">
+      <c r="A122" s="4"/>
       <c r="B122" s="1" t="s">
         <v>20</v>
       </c>
@@ -4220,22 +4360,23 @@
         <v>13</v>
       </c>
       <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>135</v>
       </c>
+      <c r="F122" s="2"/>
       <c r="G122" s="2"/>
-      <c r="H122" s="2"/>
+      <c r="H122" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I122" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J122" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J122" s="4"/>
       <c r="K122" s="4"/>
       <c r="L122" s="4"/>
     </row>
-    <row r="123" spans="2:12" ht="14">
+    <row r="123" spans="1:12" ht="14">
+      <c r="A123" s="8"/>
       <c r="B123" s="5" t="s">
         <v>3</v>
       </c>
@@ -4243,22 +4384,23 @@
         <v>13</v>
       </c>
       <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6" t="s">
+      <c r="E123" s="6" t="s">
         <v>136</v>
       </c>
+      <c r="F123" s="6"/>
       <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
+      <c r="H123" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I123" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J123" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J123" s="8"/>
       <c r="K123" s="8"/>
       <c r="L123" s="8"/>
     </row>
-    <row r="124" spans="2:12" ht="14">
+    <row r="124" spans="1:12" ht="14">
+      <c r="A124" s="4"/>
       <c r="B124" s="1" t="s">
         <v>3</v>
       </c>
@@ -4266,22 +4408,23 @@
         <v>13</v>
       </c>
       <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2" t="s">
+      <c r="E124" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="F124" s="2"/>
       <c r="G124" s="2"/>
-      <c r="H124" s="2"/>
+      <c r="H124" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I124" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J124" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
     </row>
-    <row r="125" spans="2:12" ht="14">
+    <row r="125" spans="1:12" ht="14">
+      <c r="A125" s="8"/>
       <c r="B125" s="5" t="s">
         <v>3</v>
       </c>
@@ -4289,22 +4432,23 @@
         <v>13</v>
       </c>
       <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6" t="s">
+      <c r="E125" s="6" t="s">
         <v>138</v>
       </c>
+      <c r="F125" s="6"/>
       <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
+      <c r="H125" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I125" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J125" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J125" s="8"/>
       <c r="K125" s="8"/>
       <c r="L125" s="8"/>
     </row>
-    <row r="126" spans="2:12" ht="14">
+    <row r="126" spans="1:12" ht="14">
+      <c r="A126" s="4"/>
       <c r="B126" s="1" t="s">
         <v>3</v>
       </c>
@@ -4312,22 +4456,23 @@
         <v>13</v>
       </c>
       <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2" t="s">
+      <c r="E126" s="2" t="s">
         <v>139</v>
       </c>
+      <c r="F126" s="2"/>
       <c r="G126" s="2"/>
-      <c r="H126" s="2"/>
+      <c r="H126" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I126" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J126" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J126" s="4"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
     </row>
-    <row r="127" spans="2:12" ht="14">
+    <row r="127" spans="1:12" ht="14">
+      <c r="A127" s="8"/>
       <c r="B127" s="5" t="s">
         <v>3</v>
       </c>
@@ -4335,22 +4480,23 @@
         <v>13</v>
       </c>
       <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6" t="s">
+      <c r="E127" s="6" t="s">
         <v>140</v>
       </c>
+      <c r="F127" s="6"/>
       <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
+      <c r="H127" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I127" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J127" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J127" s="8"/>
       <c r="K127" s="8"/>
       <c r="L127" s="8"/>
     </row>
-    <row r="128" spans="2:12" ht="14">
+    <row r="128" spans="1:12" ht="14">
+      <c r="A128" s="4"/>
       <c r="B128" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,22 +4504,23 @@
         <v>13</v>
       </c>
       <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2" t="s">
+      <c r="E128" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="F128" s="2"/>
       <c r="G128" s="2"/>
-      <c r="H128" s="2"/>
+      <c r="H128" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I128" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J128" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
     </row>
-    <row r="129" spans="2:12" ht="14">
+    <row r="129" spans="1:12" ht="14">
+      <c r="A129" s="8"/>
       <c r="B129" s="5" t="s">
         <v>20</v>
       </c>
@@ -4381,22 +4528,23 @@
         <v>13</v>
       </c>
       <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6" t="s">
+      <c r="E129" s="6" t="s">
         <v>142</v>
       </c>
+      <c r="F129" s="6"/>
       <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
+      <c r="H129" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I129" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J129" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J129" s="8"/>
       <c r="K129" s="8"/>
       <c r="L129" s="8"/>
     </row>
-    <row r="130" spans="2:12" ht="14">
+    <row r="130" spans="1:12" ht="14">
+      <c r="A130" s="4"/>
       <c r="B130" s="1" t="s">
         <v>20</v>
       </c>
@@ -4404,22 +4552,23 @@
         <v>13</v>
       </c>
       <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2" t="s">
+      <c r="E130" s="2" t="s">
         <v>143</v>
       </c>
+      <c r="F130" s="2"/>
       <c r="G130" s="2"/>
-      <c r="H130" s="2"/>
+      <c r="H130" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I130" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J130" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J130" s="4"/>
       <c r="K130" s="4"/>
       <c r="L130" s="4"/>
     </row>
-    <row r="131" spans="2:12" ht="14">
+    <row r="131" spans="1:12" ht="14">
+      <c r="A131" s="8"/>
       <c r="B131" s="5" t="s">
         <v>20</v>
       </c>
@@ -4427,22 +4576,23 @@
         <v>13</v>
       </c>
       <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6" t="s">
+      <c r="E131" s="6" t="s">
         <v>144</v>
       </c>
+      <c r="F131" s="6"/>
       <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
+      <c r="H131" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I131" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J131" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J131" s="8"/>
       <c r="K131" s="8"/>
       <c r="L131" s="8"/>
     </row>
-    <row r="132" spans="2:12" ht="14">
+    <row r="132" spans="1:12" ht="14">
+      <c r="A132" s="4"/>
       <c r="B132" s="1" t="s">
         <v>20</v>
       </c>
@@ -4450,22 +4600,23 @@
         <v>13</v>
       </c>
       <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2" t="s">
+      <c r="E132" s="2" t="s">
         <v>145</v>
       </c>
+      <c r="F132" s="2"/>
       <c r="G132" s="2"/>
-      <c r="H132" s="2"/>
+      <c r="H132" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I132" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J132" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J132" s="4"/>
       <c r="K132" s="4"/>
       <c r="L132" s="4"/>
     </row>
-    <row r="133" spans="2:12" ht="14">
+    <row r="133" spans="1:12" ht="14">
+      <c r="A133" s="8"/>
       <c r="B133" s="5" t="s">
         <v>20</v>
       </c>
@@ -4473,22 +4624,23 @@
         <v>13</v>
       </c>
       <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6" t="s">
+      <c r="E133" s="6" t="s">
         <v>146</v>
       </c>
+      <c r="F133" s="6"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
+      <c r="H133" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I133" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J133" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J133" s="8"/>
       <c r="K133" s="8"/>
       <c r="L133" s="8"/>
     </row>
-    <row r="134" spans="2:12" ht="14">
+    <row r="134" spans="1:12" ht="14">
+      <c r="A134" s="4"/>
       <c r="B134" s="1" t="s">
         <v>3</v>
       </c>
@@ -4496,22 +4648,23 @@
         <v>13</v>
       </c>
       <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2" t="s">
+      <c r="E134" s="2" t="s">
         <v>147</v>
       </c>
+      <c r="F134" s="2"/>
       <c r="G134" s="2"/>
-      <c r="H134" s="2"/>
+      <c r="H134" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I134" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J134" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J134" s="4"/>
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
     </row>
-    <row r="135" spans="2:12" ht="14">
+    <row r="135" spans="1:12" ht="14">
+      <c r="A135" s="8"/>
       <c r="B135" s="5" t="s">
         <v>3</v>
       </c>
@@ -4519,22 +4672,23 @@
         <v>13</v>
       </c>
       <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6" t="s">
+      <c r="E135" s="6" t="s">
         <v>148</v>
       </c>
+      <c r="F135" s="6"/>
       <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
+      <c r="H135" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I135" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J135" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J135" s="8"/>
       <c r="K135" s="8"/>
       <c r="L135" s="8"/>
     </row>
-    <row r="136" spans="2:12" ht="14">
+    <row r="136" spans="1:12" ht="14">
+      <c r="A136" s="4"/>
       <c r="B136" s="1" t="s">
         <v>3</v>
       </c>
@@ -4542,22 +4696,23 @@
         <v>13</v>
       </c>
       <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-      <c r="F136" s="2" t="s">
+      <c r="E136" s="2" t="s">
         <v>149</v>
       </c>
+      <c r="F136" s="2"/>
       <c r="G136" s="2"/>
-      <c r="H136" s="2"/>
+      <c r="H136" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I136" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J136" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J136" s="4"/>
       <c r="K136" s="4"/>
       <c r="L136" s="4"/>
     </row>
-    <row r="137" spans="2:12" ht="14">
+    <row r="137" spans="1:12" ht="14">
+      <c r="A137" s="8"/>
       <c r="B137" s="5" t="s">
         <v>3</v>
       </c>
@@ -4565,22 +4720,23 @@
         <v>13</v>
       </c>
       <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6" t="s">
+      <c r="E137" s="6" t="s">
         <v>150</v>
       </c>
+      <c r="F137" s="6"/>
       <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
+      <c r="H137" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I137" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J137" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J137" s="8"/>
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
     </row>
-    <row r="138" spans="2:12" ht="14">
+    <row r="138" spans="1:12" ht="14">
+      <c r="A138" s="4"/>
       <c r="B138" s="1" t="s">
         <v>20</v>
       </c>
@@ -4588,22 +4744,23 @@
         <v>13</v>
       </c>
       <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="F138" s="2"/>
       <c r="G138" s="2"/>
-      <c r="H138" s="2"/>
+      <c r="H138" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I138" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J138" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J138" s="4"/>
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
     </row>
-    <row r="139" spans="2:12" ht="14">
+    <row r="139" spans="1:12" ht="14">
+      <c r="A139" s="8"/>
       <c r="B139" s="5" t="s">
         <v>20</v>
       </c>
@@ -4611,22 +4768,23 @@
         <v>13</v>
       </c>
       <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6" t="s">
+      <c r="E139" s="6" t="s">
         <v>152</v>
       </c>
+      <c r="F139" s="6"/>
       <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
+      <c r="H139" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I139" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J139" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J139" s="8"/>
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
     </row>
-    <row r="140" spans="2:12" ht="14">
+    <row r="140" spans="1:12" ht="14">
+      <c r="A140" s="4"/>
       <c r="B140" s="1" t="s">
         <v>20</v>
       </c>
@@ -4634,22 +4792,23 @@
         <v>13</v>
       </c>
       <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2" t="s">
+      <c r="E140" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
+      <c r="H140" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I140" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J140" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J140" s="4"/>
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
     </row>
-    <row r="141" spans="2:12" ht="14">
+    <row r="141" spans="1:12" ht="14">
+      <c r="A141" s="8"/>
       <c r="B141" s="5" t="s">
         <v>20</v>
       </c>
@@ -4657,22 +4816,23 @@
         <v>13</v>
       </c>
       <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6" t="s">
+      <c r="E141" s="6" t="s">
         <v>154</v>
       </c>
+      <c r="F141" s="6"/>
       <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
+      <c r="H141" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I141" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J141" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J141" s="8"/>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
     </row>
-    <row r="142" spans="2:12" ht="14">
+    <row r="142" spans="1:12" ht="14">
+      <c r="A142" s="4"/>
       <c r="B142" s="1" t="s">
         <v>20</v>
       </c>
@@ -4680,22 +4840,23 @@
         <v>13</v>
       </c>
       <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2" t="s">
+      <c r="E142" s="2" t="s">
         <v>155</v>
       </c>
+      <c r="F142" s="2"/>
       <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
+      <c r="H142" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I142" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J142" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J142" s="4"/>
       <c r="K142" s="4"/>
       <c r="L142" s="4"/>
     </row>
-    <row r="143" spans="2:12" ht="14">
+    <row r="143" spans="1:12" ht="14">
+      <c r="A143" s="8"/>
       <c r="B143" s="5" t="s">
         <v>20</v>
       </c>
@@ -4703,22 +4864,23 @@
         <v>13</v>
       </c>
       <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6" t="s">
+      <c r="E143" s="6" t="s">
         <v>156</v>
       </c>
+      <c r="F143" s="6"/>
       <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
+      <c r="H143" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I143" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J143" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J143" s="8"/>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
     </row>
-    <row r="144" spans="2:12" ht="14">
+    <row r="144" spans="1:12" ht="14">
+      <c r="A144" s="4"/>
       <c r="B144" s="1" t="s">
         <v>20</v>
       </c>
@@ -4726,22 +4888,23 @@
         <v>13</v>
       </c>
       <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2" t="s">
+      <c r="E144" s="2" t="s">
         <v>157</v>
       </c>
+      <c r="F144" s="2"/>
       <c r="G144" s="2"/>
-      <c r="H144" s="2"/>
+      <c r="H144" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I144" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J144" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J144" s="4"/>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
     </row>
-    <row r="145" spans="2:12" ht="14">
+    <row r="145" spans="1:12" ht="14">
+      <c r="A145" s="8"/>
       <c r="B145" s="5" t="s">
         <v>3</v>
       </c>
@@ -4749,22 +4912,23 @@
         <v>13</v>
       </c>
       <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6" t="s">
+      <c r="E145" s="6" t="s">
         <v>158</v>
       </c>
+      <c r="F145" s="6"/>
       <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
+      <c r="H145" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I145" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J145" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J145" s="8"/>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
     </row>
-    <row r="146" spans="2:12" ht="14">
+    <row r="146" spans="1:12" ht="14">
+      <c r="A146" s="4"/>
       <c r="B146" s="1" t="s">
         <v>3</v>
       </c>
@@ -4772,22 +4936,23 @@
         <v>13</v>
       </c>
       <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
-      <c r="F146" s="2" t="s">
+      <c r="E146" s="2" t="s">
         <v>159</v>
       </c>
+      <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-      <c r="H146" s="2"/>
+      <c r="H146" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I146" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J146" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J146" s="4"/>
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
     </row>
-    <row r="147" spans="2:12" ht="14">
+    <row r="147" spans="1:12" ht="14">
+      <c r="A147" s="8"/>
       <c r="B147" s="5" t="s">
         <v>3</v>
       </c>
@@ -4795,22 +4960,23 @@
         <v>13</v>
       </c>
       <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6" t="s">
+      <c r="E147" s="6" t="s">
         <v>160</v>
       </c>
+      <c r="F147" s="6"/>
       <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
+      <c r="H147" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I147" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J147" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J147" s="8"/>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
     </row>
-    <row r="148" spans="2:12" ht="14">
+    <row r="148" spans="1:12" ht="14">
+      <c r="A148" s="4"/>
       <c r="B148" s="1" t="s">
         <v>3</v>
       </c>
@@ -4818,22 +4984,23 @@
         <v>13</v>
       </c>
       <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
-      <c r="F148" s="2" t="s">
+      <c r="E148" s="2" t="s">
         <v>161</v>
       </c>
+      <c r="F148" s="2"/>
       <c r="G148" s="2"/>
-      <c r="H148" s="2"/>
+      <c r="H148" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I148" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J148" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J148" s="4"/>
       <c r="K148" s="4"/>
       <c r="L148" s="4"/>
     </row>
-    <row r="149" spans="2:12" ht="14">
+    <row r="149" spans="1:12" ht="14">
+      <c r="A149" s="8"/>
       <c r="B149" s="5" t="s">
         <v>3</v>
       </c>
@@ -4841,22 +5008,23 @@
         <v>13</v>
       </c>
       <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6" t="s">
+      <c r="E149" s="6" t="s">
         <v>162</v>
       </c>
+      <c r="F149" s="6"/>
       <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
+      <c r="H149" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I149" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J149" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J149" s="8"/>
       <c r="K149" s="8"/>
       <c r="L149" s="8"/>
     </row>
-    <row r="150" spans="2:12" ht="14">
+    <row r="150" spans="1:12" ht="14">
+      <c r="A150" s="4"/>
       <c r="B150" s="1" t="s">
         <v>3</v>
       </c>
@@ -4864,22 +5032,23 @@
         <v>13</v>
       </c>
       <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2" t="s">
+      <c r="E150" s="2" t="s">
         <v>163</v>
       </c>
+      <c r="F150" s="2"/>
       <c r="G150" s="2"/>
-      <c r="H150" s="2"/>
+      <c r="H150" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I150" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J150" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J150" s="4"/>
       <c r="K150" s="4"/>
       <c r="L150" s="4"/>
     </row>
-    <row r="151" spans="2:12" ht="14">
+    <row r="151" spans="1:12" ht="14">
+      <c r="A151" s="8"/>
       <c r="B151" s="5" t="s">
         <v>3</v>
       </c>
@@ -4887,22 +5056,23 @@
         <v>13</v>
       </c>
       <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6" t="s">
+      <c r="E151" s="6" t="s">
         <v>164</v>
       </c>
+      <c r="F151" s="6"/>
       <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
+      <c r="H151" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I151" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J151" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J151" s="8"/>
       <c r="K151" s="8"/>
       <c r="L151" s="8"/>
     </row>
-    <row r="152" spans="2:12" ht="14">
+    <row r="152" spans="1:12" ht="14">
+      <c r="A152" s="4"/>
       <c r="B152" s="1" t="s">
         <v>3</v>
       </c>
@@ -4910,22 +5080,23 @@
         <v>13</v>
       </c>
       <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2" t="s">
+      <c r="E152" s="2" t="s">
         <v>165</v>
       </c>
+      <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-      <c r="H152" s="2"/>
+      <c r="H152" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I152" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J152" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J152" s="4"/>
       <c r="K152" s="4"/>
       <c r="L152" s="4"/>
     </row>
-    <row r="153" spans="2:12" ht="14">
+    <row r="153" spans="1:12" ht="14">
+      <c r="A153" s="8"/>
       <c r="B153" s="5" t="s">
         <v>20</v>
       </c>
@@ -4933,22 +5104,23 @@
         <v>13</v>
       </c>
       <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6" t="s">
+      <c r="E153" s="6" t="s">
         <v>166</v>
       </c>
+      <c r="F153" s="6"/>
       <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
+      <c r="H153" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I153" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J153" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J153" s="8"/>
       <c r="K153" s="8"/>
       <c r="L153" s="8"/>
     </row>
-    <row r="154" spans="2:12" ht="14">
+    <row r="154" spans="1:12" ht="14">
+      <c r="A154" s="4"/>
       <c r="B154" s="1" t="s">
         <v>20</v>
       </c>
@@ -4956,22 +5128,23 @@
         <v>13</v>
       </c>
       <c r="D154" s="2"/>
-      <c r="E154" s="2"/>
-      <c r="F154" s="2" t="s">
+      <c r="E154" s="2" t="s">
         <v>167</v>
       </c>
+      <c r="F154" s="2"/>
       <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
+      <c r="H154" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I154" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J154" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J154" s="4"/>
       <c r="K154" s="4"/>
       <c r="L154" s="4"/>
     </row>
-    <row r="155" spans="2:12" ht="14">
+    <row r="155" spans="1:12" ht="14">
+      <c r="A155" s="8"/>
       <c r="B155" s="5" t="s">
         <v>20</v>
       </c>
@@ -4979,22 +5152,23 @@
         <v>13</v>
       </c>
       <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6" t="s">
+      <c r="E155" s="6" t="s">
         <v>168</v>
       </c>
+      <c r="F155" s="6"/>
       <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
+      <c r="H155" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I155" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J155" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J155" s="8"/>
       <c r="K155" s="8"/>
       <c r="L155" s="8"/>
     </row>
-    <row r="156" spans="2:12" ht="14">
+    <row r="156" spans="1:12" ht="14">
+      <c r="A156" s="4"/>
       <c r="B156" s="1" t="s">
         <v>20</v>
       </c>
@@ -5002,22 +5176,23 @@
         <v>13</v>
       </c>
       <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
-      <c r="F156" s="2" t="s">
+      <c r="E156" s="2" t="s">
         <v>169</v>
       </c>
+      <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-      <c r="H156" s="2"/>
+      <c r="H156" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I156" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J156" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J156" s="4"/>
       <c r="K156" s="4"/>
       <c r="L156" s="4"/>
     </row>
-    <row r="157" spans="2:12" ht="14">
+    <row r="157" spans="1:12" ht="14">
+      <c r="A157" s="8"/>
       <c r="B157" s="5" t="s">
         <v>20</v>
       </c>
@@ -5025,22 +5200,23 @@
         <v>13</v>
       </c>
       <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6" t="s">
+      <c r="E157" s="6" t="s">
         <v>170</v>
       </c>
+      <c r="F157" s="6"/>
       <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
+      <c r="H157" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I157" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J157" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J157" s="8"/>
       <c r="K157" s="8"/>
       <c r="L157" s="8"/>
     </row>
-    <row r="158" spans="2:12" ht="14">
+    <row r="158" spans="1:12" ht="14">
+      <c r="A158" s="4"/>
       <c r="B158" s="1" t="s">
         <v>20</v>
       </c>
@@ -5048,22 +5224,23 @@
         <v>13</v>
       </c>
       <c r="D158" s="2"/>
-      <c r="E158" s="2"/>
-      <c r="F158" s="2" t="s">
+      <c r="E158" s="2" t="s">
         <v>171</v>
       </c>
+      <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="2"/>
+      <c r="H158" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I158" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J158" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J158" s="4"/>
       <c r="K158" s="4"/>
       <c r="L158" s="4"/>
     </row>
-    <row r="159" spans="2:12" ht="14">
+    <row r="159" spans="1:12" ht="14">
+      <c r="A159" s="8"/>
       <c r="B159" s="5" t="s">
         <v>20</v>
       </c>
@@ -5071,22 +5248,23 @@
         <v>13</v>
       </c>
       <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6" t="s">
+      <c r="E159" s="6" t="s">
         <v>172</v>
       </c>
+      <c r="F159" s="6"/>
       <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
+      <c r="H159" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I159" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J159" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J159" s="8"/>
       <c r="K159" s="8"/>
       <c r="L159" s="8"/>
     </row>
-    <row r="160" spans="2:12" ht="14">
+    <row r="160" spans="1:12" ht="14">
+      <c r="A160" s="4"/>
       <c r="B160" s="1" t="s">
         <v>3</v>
       </c>
@@ -5094,22 +5272,23 @@
         <v>13</v>
       </c>
       <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
-      <c r="F160" s="2" t="s">
+      <c r="E160" s="2" t="s">
         <v>173</v>
       </c>
+      <c r="F160" s="2"/>
       <c r="G160" s="2"/>
-      <c r="H160" s="2"/>
+      <c r="H160" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I160" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J160" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J160" s="4"/>
       <c r="K160" s="4"/>
       <c r="L160" s="4"/>
     </row>
-    <row r="161" spans="2:12" ht="14">
+    <row r="161" spans="1:12" ht="14">
+      <c r="A161" s="8"/>
       <c r="B161" s="5" t="s">
         <v>3</v>
       </c>
@@ -5117,22 +5296,23 @@
         <v>13</v>
       </c>
       <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6" t="s">
+      <c r="E161" s="6" t="s">
         <v>174</v>
       </c>
+      <c r="F161" s="6"/>
       <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
+      <c r="H161" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I161" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J161" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J161" s="8"/>
       <c r="K161" s="8"/>
       <c r="L161" s="8"/>
     </row>
-    <row r="162" spans="2:12" ht="14">
+    <row r="162" spans="1:12" ht="14">
+      <c r="A162" s="4"/>
       <c r="B162" s="1" t="s">
         <v>3</v>
       </c>
@@ -5140,22 +5320,23 @@
         <v>13</v>
       </c>
       <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2" t="s">
+      <c r="E162" s="2" t="s">
         <v>175</v>
       </c>
+      <c r="F162" s="2"/>
       <c r="G162" s="2"/>
-      <c r="H162" s="2"/>
+      <c r="H162" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I162" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J162" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J162" s="4"/>
       <c r="K162" s="4"/>
       <c r="L162" s="4"/>
     </row>
-    <row r="163" spans="2:12" ht="14">
+    <row r="163" spans="1:12" ht="14">
+      <c r="A163" s="8"/>
       <c r="B163" s="5" t="s">
         <v>3</v>
       </c>
@@ -5163,22 +5344,23 @@
         <v>13</v>
       </c>
       <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6" t="s">
+      <c r="E163" s="6" t="s">
         <v>176</v>
       </c>
+      <c r="F163" s="6"/>
       <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
+      <c r="H163" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I163" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J163" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J163" s="8"/>
       <c r="K163" s="8"/>
       <c r="L163" s="8"/>
     </row>
-    <row r="164" spans="2:12" ht="14">
+    <row r="164" spans="1:12" ht="14">
+      <c r="A164" s="4"/>
       <c r="B164" s="1" t="s">
         <v>3</v>
       </c>
@@ -5186,22 +5368,23 @@
         <v>13</v>
       </c>
       <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2" t="s">
+      <c r="E164" s="2" t="s">
         <v>177</v>
       </c>
+      <c r="F164" s="2"/>
       <c r="G164" s="2"/>
-      <c r="H164" s="2"/>
+      <c r="H164" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I164" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J164" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J164" s="4"/>
       <c r="K164" s="4"/>
       <c r="L164" s="4"/>
     </row>
-    <row r="165" spans="2:12" ht="14">
+    <row r="165" spans="1:12" ht="14">
+      <c r="A165" s="8"/>
       <c r="B165" s="5" t="s">
         <v>3</v>
       </c>
@@ -5209,22 +5392,23 @@
         <v>13</v>
       </c>
       <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6" t="s">
+      <c r="E165" s="6" t="s">
         <v>178</v>
       </c>
+      <c r="F165" s="6"/>
       <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
+      <c r="H165" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I165" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J165" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J165" s="8"/>
       <c r="K165" s="8"/>
       <c r="L165" s="8"/>
     </row>
-    <row r="166" spans="2:12" ht="14">
+    <row r="166" spans="1:12" ht="14">
+      <c r="A166" s="4"/>
       <c r="B166" s="1" t="s">
         <v>20</v>
       </c>
@@ -5232,22 +5416,23 @@
         <v>13</v>
       </c>
       <c r="D166" s="2"/>
-      <c r="E166" s="2"/>
-      <c r="F166" s="2" t="s">
+      <c r="E166" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="F166" s="2"/>
       <c r="G166" s="2"/>
-      <c r="H166" s="2"/>
+      <c r="H166" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I166" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J166" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
     </row>
-    <row r="167" spans="2:12" ht="14">
+    <row r="167" spans="1:12" ht="14">
+      <c r="A167" s="8"/>
       <c r="B167" s="5" t="s">
         <v>20</v>
       </c>
@@ -5255,22 +5440,23 @@
         <v>13</v>
       </c>
       <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6" t="s">
+      <c r="E167" s="6" t="s">
         <v>180</v>
       </c>
+      <c r="F167" s="6"/>
       <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
+      <c r="H167" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I167" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J167" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J167" s="8"/>
       <c r="K167" s="8"/>
       <c r="L167" s="8"/>
     </row>
-    <row r="168" spans="2:12" ht="14">
+    <row r="168" spans="1:12" ht="14">
+      <c r="A168" s="4"/>
       <c r="B168" s="1" t="s">
         <v>20</v>
       </c>
@@ -5278,22 +5464,23 @@
         <v>13</v>
       </c>
       <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
-      <c r="F168" s="2" t="s">
+      <c r="E168" s="2" t="s">
         <v>181</v>
       </c>
+      <c r="F168" s="2"/>
       <c r="G168" s="2"/>
-      <c r="H168" s="2"/>
+      <c r="H168" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I168" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J168" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J168" s="4"/>
       <c r="K168" s="4"/>
       <c r="L168" s="4"/>
     </row>
-    <row r="169" spans="2:12" ht="14">
+    <row r="169" spans="1:12" ht="14">
+      <c r="A169" s="8"/>
       <c r="B169" s="5" t="s">
         <v>20</v>
       </c>
@@ -5301,22 +5488,23 @@
         <v>13</v>
       </c>
       <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6" t="s">
+      <c r="E169" s="6" t="s">
         <v>182</v>
       </c>
+      <c r="F169" s="6"/>
       <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
+      <c r="H169" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I169" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J169" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J169" s="8"/>
       <c r="K169" s="8"/>
       <c r="L169" s="8"/>
     </row>
-    <row r="170" spans="2:12" ht="14">
+    <row r="170" spans="1:12" ht="14">
+      <c r="A170" s="4"/>
       <c r="B170" s="1" t="s">
         <v>20</v>
       </c>
@@ -5324,22 +5512,23 @@
         <v>13</v>
       </c>
       <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
-      <c r="F170" s="2" t="s">
+      <c r="E170" s="2" t="s">
         <v>183</v>
       </c>
+      <c r="F170" s="2"/>
       <c r="G170" s="2"/>
-      <c r="H170" s="2"/>
+      <c r="H170" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I170" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J170" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J170" s="4"/>
       <c r="K170" s="4"/>
       <c r="L170" s="4"/>
     </row>
-    <row r="171" spans="2:12" ht="14">
+    <row r="171" spans="1:12" ht="14">
+      <c r="A171" s="8"/>
       <c r="B171" s="5" t="s">
         <v>20</v>
       </c>
@@ -5347,22 +5536,23 @@
         <v>13</v>
       </c>
       <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6" t="s">
+      <c r="E171" s="6" t="s">
         <v>184</v>
       </c>
+      <c r="F171" s="6"/>
       <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
+      <c r="H171" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I171" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J171" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J171" s="8"/>
       <c r="K171" s="8"/>
       <c r="L171" s="8"/>
     </row>
-    <row r="172" spans="2:12" ht="14">
+    <row r="172" spans="1:12" ht="14">
+      <c r="A172" s="4"/>
       <c r="B172" s="1" t="s">
         <v>3</v>
       </c>
@@ -5370,22 +5560,23 @@
         <v>13</v>
       </c>
       <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2" t="s">
+      <c r="E172" s="2" t="s">
         <v>185</v>
       </c>
+      <c r="F172" s="2"/>
       <c r="G172" s="2"/>
-      <c r="H172" s="2"/>
+      <c r="H172" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I172" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J172" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J172" s="4"/>
       <c r="K172" s="4"/>
       <c r="L172" s="4"/>
     </row>
-    <row r="173" spans="2:12" ht="14">
+    <row r="173" spans="1:12" ht="14">
+      <c r="A173" s="8"/>
       <c r="B173" s="5" t="s">
         <v>3</v>
       </c>
@@ -5393,22 +5584,23 @@
         <v>13</v>
       </c>
       <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6" t="s">
+      <c r="E173" s="6" t="s">
         <v>186</v>
       </c>
+      <c r="F173" s="6"/>
       <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
+      <c r="H173" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I173" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J173" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J173" s="8"/>
       <c r="K173" s="8"/>
       <c r="L173" s="8"/>
     </row>
-    <row r="174" spans="2:12" ht="14">
+    <row r="174" spans="1:12" ht="14">
+      <c r="A174" s="4"/>
       <c r="B174" s="1" t="s">
         <v>3</v>
       </c>
@@ -5416,22 +5608,23 @@
         <v>13</v>
       </c>
       <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2" t="s">
+      <c r="E174" s="2" t="s">
         <v>187</v>
       </c>
+      <c r="F174" s="2"/>
       <c r="G174" s="2"/>
-      <c r="H174" s="2"/>
+      <c r="H174" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I174" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J174" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J174" s="4"/>
       <c r="K174" s="4"/>
       <c r="L174" s="4"/>
     </row>
-    <row r="175" spans="2:12" ht="14">
+    <row r="175" spans="1:12" ht="14">
+      <c r="A175" s="8"/>
       <c r="B175" s="5" t="s">
         <v>3</v>
       </c>
@@ -5439,22 +5632,23 @@
         <v>13</v>
       </c>
       <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6" t="s">
+      <c r="E175" s="6" t="s">
         <v>188</v>
       </c>
+      <c r="F175" s="6"/>
       <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
+      <c r="H175" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I175" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J175" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J175" s="8"/>
       <c r="K175" s="8"/>
       <c r="L175" s="8"/>
     </row>
-    <row r="176" spans="2:12" ht="14">
+    <row r="176" spans="1:12" ht="14">
+      <c r="A176" s="4"/>
       <c r="B176" s="1" t="s">
         <v>20</v>
       </c>
@@ -5462,22 +5656,23 @@
         <v>13</v>
       </c>
       <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="2" t="s">
+      <c r="E176" s="2" t="s">
         <v>189</v>
       </c>
+      <c r="F176" s="2"/>
       <c r="G176" s="2"/>
-      <c r="H176" s="2"/>
+      <c r="H176" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I176" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J176" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J176" s="4"/>
       <c r="K176" s="4"/>
       <c r="L176" s="4"/>
     </row>
-    <row r="177" spans="2:12" ht="14">
+    <row r="177" spans="1:12" ht="14">
+      <c r="A177" s="8"/>
       <c r="B177" s="5" t="s">
         <v>20</v>
       </c>
@@ -5485,22 +5680,23 @@
         <v>13</v>
       </c>
       <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6" t="s">
+      <c r="E177" s="6" t="s">
         <v>190</v>
       </c>
+      <c r="F177" s="6"/>
       <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
+      <c r="H177" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I177" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J177" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J177" s="8"/>
       <c r="K177" s="8"/>
       <c r="L177" s="8"/>
     </row>
-    <row r="178" spans="2:12" ht="14">
+    <row r="178" spans="1:12" ht="14">
+      <c r="A178" s="4"/>
       <c r="B178" s="1" t="s">
         <v>20</v>
       </c>
@@ -5508,22 +5704,23 @@
         <v>13</v>
       </c>
       <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="2" t="s">
+      <c r="E178" s="2" t="s">
         <v>191</v>
       </c>
+      <c r="F178" s="2"/>
       <c r="G178" s="2"/>
-      <c r="H178" s="2"/>
+      <c r="H178" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I178" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J178" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J178" s="4"/>
       <c r="K178" s="4"/>
       <c r="L178" s="4"/>
     </row>
-    <row r="179" spans="2:12" ht="14">
+    <row r="179" spans="1:12" ht="14">
+      <c r="A179" s="8"/>
       <c r="B179" s="5" t="s">
         <v>20</v>
       </c>
@@ -5531,22 +5728,23 @@
         <v>13</v>
       </c>
       <c r="D179" s="21"/>
-      <c r="E179" s="21"/>
-      <c r="F179" s="6" t="s">
+      <c r="E179" s="6" t="s">
         <v>192</v>
       </c>
+      <c r="F179" s="6"/>
       <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
+      <c r="H179" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I179" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J179" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J179" s="8"/>
       <c r="K179" s="8"/>
       <c r="L179" s="8"/>
     </row>
-    <row r="180" spans="2:12" ht="14">
+    <row r="180" spans="1:12" ht="14">
+      <c r="A180" s="4"/>
       <c r="B180" s="1" t="s">
         <v>20</v>
       </c>
@@ -5554,22 +5752,23 @@
         <v>13</v>
       </c>
       <c r="D180" s="22"/>
-      <c r="E180" s="22"/>
-      <c r="F180" s="2" t="s">
+      <c r="E180" s="2" t="s">
         <v>193</v>
       </c>
+      <c r="F180" s="2"/>
       <c r="G180" s="2"/>
-      <c r="H180" s="2"/>
+      <c r="H180" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I180" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J180" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J180" s="4"/>
       <c r="K180" s="4"/>
       <c r="L180" s="4"/>
     </row>
-    <row r="181" spans="2:12" ht="14">
+    <row r="181" spans="1:12" ht="14">
+      <c r="A181" s="8"/>
       <c r="B181" s="5" t="s">
         <v>3</v>
       </c>
@@ -5577,22 +5776,23 @@
         <v>13</v>
       </c>
       <c r="D181" s="21"/>
-      <c r="E181" s="21"/>
-      <c r="F181" s="6" t="s">
+      <c r="E181" s="6" t="s">
         <v>194</v>
       </c>
+      <c r="F181" s="6"/>
       <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
+      <c r="H181" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I181" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J181" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J181" s="8"/>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
     </row>
-    <row r="182" spans="2:12" ht="14">
+    <row r="182" spans="1:12" ht="14">
+      <c r="A182" s="4"/>
       <c r="B182" s="1" t="s">
         <v>20</v>
       </c>
@@ -5600,22 +5800,23 @@
         <v>13</v>
       </c>
       <c r="D182" s="22"/>
-      <c r="E182" s="22"/>
-      <c r="F182" s="2" t="s">
+      <c r="E182" s="2" t="s">
         <v>195</v>
       </c>
+      <c r="F182" s="2"/>
       <c r="G182" s="2"/>
-      <c r="H182" s="2"/>
+      <c r="H182" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I182" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J182" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J182" s="4"/>
       <c r="K182" s="4"/>
       <c r="L182" s="4"/>
     </row>
-    <row r="183" spans="2:12" ht="14">
+    <row r="183" spans="1:12" ht="14">
+      <c r="A183" s="8"/>
       <c r="B183" s="5" t="s">
         <v>3</v>
       </c>
@@ -5623,22 +5824,23 @@
         <v>13</v>
       </c>
       <c r="D183" s="21"/>
-      <c r="E183" s="21"/>
-      <c r="F183" s="6" t="s">
+      <c r="E183" s="6" t="s">
         <v>196</v>
       </c>
+      <c r="F183" s="6"/>
       <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
+      <c r="H183" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I183" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J183" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J183" s="8"/>
       <c r="K183" s="8"/>
       <c r="L183" s="8"/>
     </row>
-    <row r="184" spans="2:12" ht="14">
+    <row r="184" spans="1:12" ht="14">
+      <c r="A184" s="4"/>
       <c r="B184" s="1" t="s">
         <v>20</v>
       </c>
@@ -5646,22 +5848,23 @@
         <v>13</v>
       </c>
       <c r="D184" s="22"/>
-      <c r="E184" s="22"/>
-      <c r="F184" s="2" t="s">
+      <c r="E184" s="2" t="s">
         <v>197</v>
       </c>
+      <c r="F184" s="2"/>
       <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
+      <c r="H184" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I184" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J184" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J184" s="4"/>
       <c r="K184" s="4"/>
       <c r="L184" s="4"/>
     </row>
-    <row r="185" spans="2:12" ht="14">
+    <row r="185" spans="1:12" ht="14">
+      <c r="A185" s="8"/>
       <c r="B185" s="5" t="s">
         <v>3</v>
       </c>
@@ -5669,22 +5872,23 @@
         <v>198</v>
       </c>
       <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="12" t="s">
+      <c r="E185" s="12" t="s">
         <v>199</v>
       </c>
+      <c r="F185" s="12"/>
       <c r="G185" s="12"/>
-      <c r="H185" s="12"/>
+      <c r="H185" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I185" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J185" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J185" s="8"/>
       <c r="K185" s="8"/>
       <c r="L185" s="8"/>
     </row>
-    <row r="186" spans="2:12" ht="14">
+    <row r="186" spans="1:12" ht="14">
+      <c r="A186" s="4"/>
       <c r="B186" s="1" t="s">
         <v>3</v>
       </c>
@@ -5692,22 +5896,23 @@
         <v>198</v>
       </c>
       <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="13" t="s">
+      <c r="E186" s="13" t="s">
         <v>200</v>
       </c>
+      <c r="F186" s="13"/>
       <c r="G186" s="13"/>
-      <c r="H186" s="13"/>
+      <c r="H186" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I186" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J186" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J186" s="4"/>
       <c r="K186" s="4"/>
       <c r="L186" s="4"/>
     </row>
-    <row r="187" spans="2:12" ht="14">
+    <row r="187" spans="1:12" ht="14">
+      <c r="A187" s="8"/>
       <c r="B187" s="5" t="s">
         <v>3</v>
       </c>
@@ -5715,22 +5920,23 @@
         <v>198</v>
       </c>
       <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="12" t="s">
+      <c r="E187" s="12" t="s">
         <v>201</v>
       </c>
+      <c r="F187" s="12"/>
       <c r="G187" s="12"/>
-      <c r="H187" s="12"/>
+      <c r="H187" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I187" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J187" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J187" s="8"/>
       <c r="K187" s="8"/>
       <c r="L187" s="8"/>
     </row>
-    <row r="188" spans="2:12" ht="14">
+    <row r="188" spans="1:12" ht="14">
+      <c r="A188" s="4"/>
       <c r="B188" s="1" t="s">
         <v>3</v>
       </c>
@@ -5738,22 +5944,23 @@
         <v>198</v>
       </c>
       <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
-      <c r="F188" s="13" t="s">
+      <c r="E188" s="13" t="s">
         <v>202</v>
       </c>
+      <c r="F188" s="13"/>
       <c r="G188" s="13"/>
-      <c r="H188" s="13"/>
+      <c r="H188" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I188" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J188" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J188" s="4"/>
       <c r="K188" s="4"/>
       <c r="L188" s="4"/>
     </row>
-    <row r="189" spans="2:12" ht="14">
+    <row r="189" spans="1:12" ht="14">
+      <c r="A189" s="8"/>
       <c r="B189" s="5" t="s">
         <v>3</v>
       </c>
@@ -5761,22 +5968,23 @@
         <v>198</v>
       </c>
       <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="12" t="s">
+      <c r="E189" s="12" t="s">
         <v>203</v>
       </c>
+      <c r="F189" s="12"/>
       <c r="G189" s="12"/>
-      <c r="H189" s="12"/>
+      <c r="H189" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I189" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J189" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J189" s="8"/>
       <c r="K189" s="8"/>
       <c r="L189" s="8"/>
     </row>
-    <row r="190" spans="2:12" ht="14">
+    <row r="190" spans="1:12" ht="14">
+      <c r="A190" s="4"/>
       <c r="B190" s="1" t="s">
         <v>3</v>
       </c>
@@ -5784,22 +5992,23 @@
         <v>198</v>
       </c>
       <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
-      <c r="F190" s="13" t="s">
+      <c r="E190" s="13" t="s">
         <v>204</v>
       </c>
+      <c r="F190" s="13"/>
       <c r="G190" s="13"/>
-      <c r="H190" s="13"/>
+      <c r="H190" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I190" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J190" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J190" s="4"/>
       <c r="K190" s="4"/>
       <c r="L190" s="4"/>
     </row>
-    <row r="191" spans="2:12" ht="14">
+    <row r="191" spans="1:12" ht="14">
+      <c r="A191" s="8"/>
       <c r="B191" s="5" t="s">
         <v>3</v>
       </c>
@@ -5807,22 +6016,23 @@
         <v>198</v>
       </c>
       <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="12" t="s">
+      <c r="E191" s="12" t="s">
         <v>205</v>
       </c>
+      <c r="F191" s="12"/>
       <c r="G191" s="12"/>
-      <c r="H191" s="12"/>
+      <c r="H191" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I191" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J191" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J191" s="8"/>
       <c r="K191" s="8"/>
       <c r="L191" s="8"/>
     </row>
-    <row r="192" spans="2:12" ht="14">
+    <row r="192" spans="1:12" ht="14">
+      <c r="A192" s="4"/>
       <c r="B192" s="1" t="s">
         <v>3</v>
       </c>
@@ -5830,22 +6040,23 @@
         <v>198</v>
       </c>
       <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
-      <c r="F192" s="13" t="s">
+      <c r="E192" s="13" t="s">
         <v>206</v>
       </c>
+      <c r="F192" s="13"/>
       <c r="G192" s="13"/>
-      <c r="H192" s="13"/>
+      <c r="H192" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I192" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J192" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J192" s="4"/>
       <c r="K192" s="4"/>
       <c r="L192" s="4"/>
     </row>
-    <row r="193" spans="2:12" ht="14">
+    <row r="193" spans="1:12" ht="14">
+      <c r="A193" s="8"/>
       <c r="B193" s="5" t="s">
         <v>3</v>
       </c>
@@ -5853,22 +6064,23 @@
         <v>198</v>
       </c>
       <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="12" t="s">
+      <c r="E193" s="12" t="s">
         <v>207</v>
       </c>
+      <c r="F193" s="12"/>
       <c r="G193" s="12"/>
-      <c r="H193" s="12"/>
+      <c r="H193" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I193" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J193" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J193" s="8"/>
       <c r="K193" s="8"/>
       <c r="L193" s="8"/>
     </row>
-    <row r="194" spans="2:12" ht="14">
+    <row r="194" spans="1:12" ht="14">
+      <c r="A194" s="4"/>
       <c r="B194" s="1" t="s">
         <v>3</v>
       </c>
@@ -5876,22 +6088,23 @@
         <v>198</v>
       </c>
       <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
-      <c r="F194" s="13" t="s">
+      <c r="E194" s="13" t="s">
         <v>208</v>
       </c>
+      <c r="F194" s="13"/>
       <c r="G194" s="13"/>
-      <c r="H194" s="13"/>
+      <c r="H194" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I194" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J194" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J194" s="4"/>
       <c r="K194" s="4"/>
       <c r="L194" s="4"/>
     </row>
-    <row r="195" spans="2:12" ht="14">
+    <row r="195" spans="1:12" ht="14">
+      <c r="A195" s="8"/>
       <c r="B195" s="5" t="s">
         <v>3</v>
       </c>
@@ -5899,22 +6112,23 @@
         <v>198</v>
       </c>
       <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="12" t="s">
+      <c r="E195" s="12" t="s">
         <v>209</v>
       </c>
+      <c r="F195" s="12"/>
       <c r="G195" s="12"/>
-      <c r="H195" s="12"/>
+      <c r="H195" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I195" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J195" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J195" s="8"/>
       <c r="K195" s="8"/>
       <c r="L195" s="8"/>
     </row>
-    <row r="196" spans="2:12" ht="14">
+    <row r="196" spans="1:12" ht="14">
+      <c r="A196" s="4"/>
       <c r="B196" s="1" t="s">
         <v>3</v>
       </c>
@@ -5922,22 +6136,23 @@
         <v>198</v>
       </c>
       <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
-      <c r="F196" s="13" t="s">
+      <c r="E196" s="13" t="s">
         <v>210</v>
       </c>
+      <c r="F196" s="13"/>
       <c r="G196" s="13"/>
-      <c r="H196" s="13"/>
+      <c r="H196" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I196" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J196" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J196" s="4"/>
       <c r="K196" s="4"/>
       <c r="L196" s="4"/>
     </row>
-    <row r="197" spans="2:12" ht="14">
+    <row r="197" spans="1:12" ht="14">
+      <c r="A197" s="8"/>
       <c r="B197" s="5" t="s">
         <v>3</v>
       </c>
@@ -5945,22 +6160,23 @@
         <v>198</v>
       </c>
       <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="12" t="s">
+      <c r="E197" s="12" t="s">
         <v>211</v>
       </c>
+      <c r="F197" s="12"/>
       <c r="G197" s="12"/>
-      <c r="H197" s="12"/>
+      <c r="H197" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I197" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J197" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J197" s="8"/>
       <c r="K197" s="8"/>
       <c r="L197" s="8"/>
     </row>
-    <row r="198" spans="2:12" ht="14">
+    <row r="198" spans="1:12" ht="14">
+      <c r="A198" s="4"/>
       <c r="B198" s="1" t="s">
         <v>3</v>
       </c>
@@ -5968,22 +6184,23 @@
         <v>198</v>
       </c>
       <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
-      <c r="F198" s="13" t="s">
+      <c r="E198" s="13" t="s">
         <v>212</v>
       </c>
+      <c r="F198" s="13"/>
       <c r="G198" s="13"/>
-      <c r="H198" s="13"/>
+      <c r="H198" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I198" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J198" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J198" s="4"/>
       <c r="K198" s="4"/>
       <c r="L198" s="4"/>
     </row>
-    <row r="199" spans="2:12" ht="14">
+    <row r="199" spans="1:12" ht="14">
+      <c r="A199" s="8"/>
       <c r="B199" s="5" t="s">
         <v>3</v>
       </c>
@@ -5991,22 +6208,23 @@
         <v>198</v>
       </c>
       <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="12" t="s">
+      <c r="E199" s="12" t="s">
         <v>213</v>
       </c>
+      <c r="F199" s="12"/>
       <c r="G199" s="12"/>
-      <c r="H199" s="12"/>
+      <c r="H199" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I199" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J199" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J199" s="8"/>
       <c r="K199" s="8"/>
       <c r="L199" s="8"/>
     </row>
-    <row r="200" spans="2:12" ht="14">
+    <row r="200" spans="1:12" ht="14">
+      <c r="A200" s="4"/>
       <c r="B200" s="1" t="s">
         <v>3</v>
       </c>
@@ -6014,22 +6232,23 @@
         <v>198</v>
       </c>
       <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="13" t="s">
+      <c r="E200" s="13" t="s">
         <v>214</v>
       </c>
+      <c r="F200" s="13"/>
       <c r="G200" s="13"/>
-      <c r="H200" s="13"/>
+      <c r="H200" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I200" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J200" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J200" s="4"/>
       <c r="K200" s="4"/>
       <c r="L200" s="4"/>
     </row>
-    <row r="201" spans="2:12" ht="14">
+    <row r="201" spans="1:12" ht="14">
+      <c r="A201" s="8"/>
       <c r="B201" s="5" t="s">
         <v>3</v>
       </c>
@@ -6037,22 +6256,23 @@
         <v>198</v>
       </c>
       <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="12" t="s">
+      <c r="E201" s="12" t="s">
         <v>215</v>
       </c>
+      <c r="F201" s="12"/>
       <c r="G201" s="12"/>
-      <c r="H201" s="12"/>
+      <c r="H201" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I201" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J201" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J201" s="8"/>
       <c r="K201" s="8"/>
       <c r="L201" s="8"/>
     </row>
-    <row r="202" spans="2:12" ht="14">
+    <row r="202" spans="1:12" ht="14">
+      <c r="A202" s="4"/>
       <c r="B202" s="1" t="s">
         <v>3</v>
       </c>
@@ -6060,22 +6280,23 @@
         <v>216</v>
       </c>
       <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
-      <c r="F202" s="13" t="s">
+      <c r="E202" s="13" t="s">
         <v>217</v>
       </c>
+      <c r="F202" s="13"/>
       <c r="G202" s="13"/>
-      <c r="H202" s="13"/>
+      <c r="H202" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I202" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J202" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J202" s="4"/>
       <c r="K202" s="4"/>
       <c r="L202" s="4"/>
     </row>
-    <row r="203" spans="2:12" ht="14">
+    <row r="203" spans="1:12" ht="14">
+      <c r="A203" s="8"/>
       <c r="B203" s="5" t="s">
         <v>3</v>
       </c>
@@ -6083,22 +6304,23 @@
         <v>216</v>
       </c>
       <c r="D203" s="6"/>
-      <c r="E203" s="6"/>
-      <c r="F203" s="12" t="s">
+      <c r="E203" s="12" t="s">
         <v>218</v>
       </c>
+      <c r="F203" s="12"/>
       <c r="G203" s="12"/>
-      <c r="H203" s="12"/>
+      <c r="H203" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I203" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J203" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J203" s="8"/>
       <c r="K203" s="8"/>
       <c r="L203" s="8"/>
     </row>
-    <row r="204" spans="2:12" ht="14">
+    <row r="204" spans="1:12" ht="14">
+      <c r="A204" s="4"/>
       <c r="B204" s="1" t="s">
         <v>3</v>
       </c>
@@ -6106,22 +6328,23 @@
         <v>216</v>
       </c>
       <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="13" t="s">
+      <c r="E204" s="13" t="s">
         <v>219</v>
       </c>
+      <c r="F204" s="13"/>
       <c r="G204" s="13"/>
-      <c r="H204" s="13"/>
+      <c r="H204" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I204" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J204" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J204" s="4"/>
       <c r="K204" s="4"/>
       <c r="L204" s="4"/>
     </row>
-    <row r="205" spans="2:12" ht="14">
+    <row r="205" spans="1:12" ht="14">
+      <c r="A205" s="8"/>
       <c r="B205" s="5" t="s">
         <v>3</v>
       </c>
@@ -6129,22 +6352,23 @@
         <v>216</v>
       </c>
       <c r="D205" s="6"/>
-      <c r="E205" s="6"/>
-      <c r="F205" s="12" t="s">
+      <c r="E205" s="12" t="s">
         <v>220</v>
       </c>
+      <c r="F205" s="12"/>
       <c r="G205" s="12"/>
-      <c r="H205" s="12"/>
+      <c r="H205" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I205" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J205" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J205" s="8"/>
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
     </row>
-    <row r="206" spans="2:12" ht="14">
+    <row r="206" spans="1:12" ht="14">
+      <c r="A206" s="4"/>
       <c r="B206" s="1" t="s">
         <v>3</v>
       </c>
@@ -6152,22 +6376,23 @@
         <v>216</v>
       </c>
       <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
-      <c r="F206" s="13" t="s">
+      <c r="E206" s="13" t="s">
         <v>221</v>
       </c>
+      <c r="F206" s="13"/>
       <c r="G206" s="13"/>
-      <c r="H206" s="13"/>
+      <c r="H206" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I206" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J206" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J206" s="4"/>
       <c r="K206" s="4"/>
       <c r="L206" s="4"/>
     </row>
-    <row r="207" spans="2:12" ht="14">
+    <row r="207" spans="1:12" ht="14">
+      <c r="A207" s="8"/>
       <c r="B207" s="5" t="s">
         <v>3</v>
       </c>
@@ -6175,22 +6400,23 @@
         <v>216</v>
       </c>
       <c r="D207" s="6"/>
-      <c r="E207" s="6"/>
-      <c r="F207" s="12" t="s">
+      <c r="E207" s="12" t="s">
         <v>222</v>
       </c>
+      <c r="F207" s="12"/>
       <c r="G207" s="12"/>
-      <c r="H207" s="12"/>
+      <c r="H207" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I207" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J207" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J207" s="8"/>
       <c r="K207" s="8"/>
       <c r="L207" s="8"/>
     </row>
-    <row r="208" spans="2:12" ht="14">
+    <row r="208" spans="1:12" ht="14">
+      <c r="A208" s="4"/>
       <c r="B208" s="1" t="s">
         <v>3</v>
       </c>
@@ -6198,22 +6424,23 @@
         <v>216</v>
       </c>
       <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="13" t="s">
+      <c r="E208" s="13" t="s">
         <v>223</v>
       </c>
+      <c r="F208" s="13"/>
       <c r="G208" s="13"/>
-      <c r="H208" s="13"/>
+      <c r="H208" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I208" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J208" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J208" s="4"/>
       <c r="K208" s="4"/>
       <c r="L208" s="4"/>
     </row>
-    <row r="209" spans="2:12" ht="14">
+    <row r="209" spans="1:12" ht="14">
+      <c r="A209" s="8"/>
       <c r="B209" s="5" t="s">
         <v>3</v>
       </c>
@@ -6221,22 +6448,23 @@
         <v>216</v>
       </c>
       <c r="D209" s="6"/>
-      <c r="E209" s="6"/>
-      <c r="F209" s="12" t="s">
+      <c r="E209" s="12" t="s">
         <v>224</v>
       </c>
+      <c r="F209" s="12"/>
       <c r="G209" s="12"/>
-      <c r="H209" s="12"/>
+      <c r="H209" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I209" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J209" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J209" s="8"/>
       <c r="K209" s="8"/>
       <c r="L209" s="8"/>
     </row>
-    <row r="210" spans="2:12" ht="14">
+    <row r="210" spans="1:12" ht="14">
+      <c r="A210" s="4"/>
       <c r="B210" s="1" t="s">
         <v>3</v>
       </c>
@@ -6244,22 +6472,23 @@
         <v>225</v>
       </c>
       <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="4" t="s">
+      <c r="E210" s="4" t="s">
         <v>226</v>
       </c>
+      <c r="F210" s="4"/>
       <c r="G210" s="4"/>
-      <c r="H210" s="4"/>
+      <c r="H210" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I210" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J210" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J210" s="4"/>
       <c r="K210" s="4"/>
       <c r="L210" s="4"/>
     </row>
-    <row r="211" spans="2:12" ht="14">
+    <row r="211" spans="1:12" ht="14">
+      <c r="A211" s="8"/>
       <c r="B211" s="14" t="s">
         <v>3</v>
       </c>
@@ -6267,22 +6496,23 @@
         <v>225</v>
       </c>
       <c r="D211" s="6"/>
-      <c r="E211" s="6"/>
-      <c r="F211" s="8" t="s">
+      <c r="E211" s="8" t="s">
         <v>227</v>
       </c>
+      <c r="F211" s="8"/>
       <c r="G211" s="8"/>
-      <c r="H211" s="8"/>
+      <c r="H211" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I211" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J211" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J211" s="8"/>
       <c r="K211" s="15"/>
       <c r="L211" s="15"/>
     </row>
-    <row r="212" spans="2:12" ht="14">
+    <row r="212" spans="1:12" ht="14">
+      <c r="A212" s="4"/>
       <c r="B212" s="16" t="s">
         <v>20</v>
       </c>
@@ -6290,22 +6520,23 @@
         <v>225</v>
       </c>
       <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="4" t="s">
+      <c r="E212" s="4" t="s">
         <v>228</v>
       </c>
+      <c r="F212" s="4"/>
       <c r="G212" s="4"/>
-      <c r="H212" s="4"/>
+      <c r="H212" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I212" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J212" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J212" s="4"/>
       <c r="K212" s="17"/>
       <c r="L212" s="17"/>
     </row>
-    <row r="213" spans="2:12" ht="14">
+    <row r="213" spans="1:12" ht="14">
+      <c r="A213" s="8"/>
       <c r="B213" s="14" t="s">
         <v>20</v>
       </c>
@@ -6313,22 +6544,23 @@
         <v>225</v>
       </c>
       <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="8" t="s">
+      <c r="E213" s="8" t="s">
         <v>229</v>
       </c>
+      <c r="F213" s="8"/>
       <c r="G213" s="8"/>
-      <c r="H213" s="8"/>
+      <c r="H213" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I213" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J213" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J213" s="8"/>
       <c r="K213" s="15"/>
       <c r="L213" s="15"/>
     </row>
-    <row r="214" spans="2:12" ht="14">
+    <row r="214" spans="1:12" ht="14">
+      <c r="A214" s="4"/>
       <c r="B214" s="16" t="s">
         <v>20</v>
       </c>
@@ -6336,22 +6568,23 @@
         <v>225</v>
       </c>
       <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="4" t="s">
+      <c r="E214" s="4" t="s">
         <v>230</v>
       </c>
+      <c r="F214" s="4"/>
       <c r="G214" s="4"/>
-      <c r="H214" s="4"/>
+      <c r="H214" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I214" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J214" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J214" s="4"/>
       <c r="K214" s="17"/>
       <c r="L214" s="17"/>
     </row>
-    <row r="215" spans="2:12" ht="14">
+    <row r="215" spans="1:12" ht="14">
+      <c r="A215" s="8"/>
       <c r="B215" s="14" t="s">
         <v>20</v>
       </c>
@@ -6359,22 +6592,23 @@
         <v>225</v>
       </c>
       <c r="D215" s="6"/>
-      <c r="E215" s="6"/>
-      <c r="F215" s="8" t="s">
+      <c r="E215" s="8" t="s">
         <v>231</v>
       </c>
+      <c r="F215" s="8"/>
       <c r="G215" s="8"/>
-      <c r="H215" s="8"/>
+      <c r="H215" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I215" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J215" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J215" s="8"/>
       <c r="K215" s="15"/>
       <c r="L215" s="15"/>
     </row>
-    <row r="216" spans="2:12" ht="14">
+    <row r="216" spans="1:12" ht="14">
+      <c r="A216" s="4"/>
       <c r="B216" s="16" t="s">
         <v>20</v>
       </c>
@@ -6382,22 +6616,23 @@
         <v>225</v>
       </c>
       <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-      <c r="F216" s="4" t="s">
+      <c r="E216" s="4" t="s">
         <v>232</v>
       </c>
+      <c r="F216" s="4"/>
       <c r="G216" s="4"/>
-      <c r="H216" s="4"/>
+      <c r="H216" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I216" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J216" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J216" s="4"/>
       <c r="K216" s="17"/>
       <c r="L216" s="17"/>
     </row>
-    <row r="217" spans="2:12" ht="14">
+    <row r="217" spans="1:12" ht="14">
+      <c r="A217" s="8"/>
       <c r="B217" s="14" t="s">
         <v>3</v>
       </c>
@@ -6405,22 +6640,23 @@
         <v>225</v>
       </c>
       <c r="D217" s="6"/>
-      <c r="E217" s="6"/>
-      <c r="F217" s="8" t="s">
+      <c r="E217" s="8" t="s">
         <v>233</v>
       </c>
+      <c r="F217" s="8"/>
       <c r="G217" s="8"/>
-      <c r="H217" s="8"/>
+      <c r="H217" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I217" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J217" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J217" s="8"/>
       <c r="K217" s="15"/>
       <c r="L217" s="15"/>
     </row>
-    <row r="218" spans="2:12" ht="13">
+    <row r="218" spans="1:12" ht="13">
+      <c r="A218" s="4"/>
       <c r="B218" s="16" t="s">
         <v>20</v>
       </c>
@@ -6428,22 +6664,23 @@
         <v>225</v>
       </c>
       <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="17" t="s">
+      <c r="E218" s="17" t="s">
         <v>234</v>
       </c>
+      <c r="F218" s="17"/>
       <c r="G218" s="17"/>
-      <c r="H218" s="17"/>
+      <c r="H218" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I218" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J218" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J218" s="4"/>
       <c r="K218" s="17"/>
       <c r="L218" s="17"/>
     </row>
-    <row r="219" spans="2:12" ht="13">
+    <row r="219" spans="1:12" ht="13">
+      <c r="A219" s="8"/>
       <c r="B219" s="14" t="s">
         <v>8</v>
       </c>
@@ -6451,22 +6688,23 @@
         <v>235</v>
       </c>
       <c r="D219" s="6"/>
-      <c r="E219" s="6"/>
-      <c r="F219" s="15" t="s">
+      <c r="E219" s="15" t="s">
         <v>236</v>
       </c>
+      <c r="F219" s="15"/>
       <c r="G219" s="15"/>
-      <c r="H219" s="15"/>
+      <c r="H219" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I219" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J219" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J219" s="8"/>
       <c r="K219" s="15"/>
       <c r="L219" s="15"/>
     </row>
-    <row r="220" spans="2:12" ht="13">
+    <row r="220" spans="1:12" ht="13">
+      <c r="A220" s="4"/>
       <c r="B220" s="16" t="s">
         <v>8</v>
       </c>
@@ -6474,22 +6712,23 @@
         <v>235</v>
       </c>
       <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="17" t="s">
+      <c r="E220" s="17" t="s">
         <v>237</v>
       </c>
+      <c r="F220" s="17"/>
       <c r="G220" s="17"/>
-      <c r="H220" s="17"/>
+      <c r="H220" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I220" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J220" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J220" s="4"/>
       <c r="K220" s="17"/>
       <c r="L220" s="17"/>
     </row>
-    <row r="221" spans="2:12" ht="13">
+    <row r="221" spans="1:12" ht="13">
+      <c r="A221" s="8"/>
       <c r="B221" s="14" t="s">
         <v>8</v>
       </c>
@@ -6497,22 +6736,23 @@
         <v>235</v>
       </c>
       <c r="D221" s="6"/>
-      <c r="E221" s="6"/>
-      <c r="F221" s="15" t="s">
+      <c r="E221" s="15" t="s">
         <v>238</v>
       </c>
+      <c r="F221" s="15"/>
       <c r="G221" s="15"/>
-      <c r="H221" s="15"/>
+      <c r="H221" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I221" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J221" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J221" s="8"/>
       <c r="K221" s="15"/>
       <c r="L221" s="15"/>
     </row>
-    <row r="222" spans="2:12" ht="13">
+    <row r="222" spans="1:12" ht="13">
+      <c r="A222" s="4"/>
       <c r="B222" s="16" t="s">
         <v>8</v>
       </c>
@@ -6520,22 +6760,23 @@
         <v>235</v>
       </c>
       <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="17" t="s">
+      <c r="E222" s="17" t="s">
         <v>239</v>
       </c>
+      <c r="F222" s="17"/>
       <c r="G222" s="17"/>
-      <c r="H222" s="17"/>
+      <c r="H222" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I222" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J222" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J222" s="4"/>
       <c r="K222" s="17"/>
       <c r="L222" s="17"/>
     </row>
-    <row r="223" spans="2:12" ht="13">
+    <row r="223" spans="1:12" ht="13">
+      <c r="A223" s="8"/>
       <c r="B223" s="14" t="s">
         <v>8</v>
       </c>
@@ -6543,22 +6784,23 @@
         <v>235</v>
       </c>
       <c r="D223" s="6"/>
-      <c r="E223" s="6"/>
-      <c r="F223" s="15" t="s">
+      <c r="E223" s="15" t="s">
         <v>240</v>
       </c>
+      <c r="F223" s="15"/>
       <c r="G223" s="15"/>
-      <c r="H223" s="15"/>
+      <c r="H223" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I223" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J223" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J223" s="8"/>
       <c r="K223" s="15"/>
       <c r="L223" s="15"/>
     </row>
-    <row r="224" spans="2:12" ht="13">
+    <row r="224" spans="1:12" ht="13">
+      <c r="A224" s="4"/>
       <c r="B224" s="16" t="s">
         <v>8</v>
       </c>
@@ -6566,22 +6808,23 @@
         <v>235</v>
       </c>
       <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="17" t="s">
+      <c r="E224" s="17" t="s">
         <v>241</v>
       </c>
+      <c r="F224" s="17"/>
       <c r="G224" s="17"/>
-      <c r="H224" s="17"/>
+      <c r="H224" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I224" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J224" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J224" s="4"/>
       <c r="K224" s="17"/>
       <c r="L224" s="17"/>
     </row>
-    <row r="225" spans="2:12" ht="13">
+    <row r="225" spans="1:12" ht="13">
+      <c r="A225" s="8"/>
       <c r="B225" s="14" t="s">
         <v>8</v>
       </c>
@@ -6589,22 +6832,23 @@
         <v>235</v>
       </c>
       <c r="D225" s="6"/>
-      <c r="E225" s="6"/>
-      <c r="F225" s="15" t="s">
+      <c r="E225" s="15" t="s">
         <v>242</v>
       </c>
+      <c r="F225" s="15"/>
       <c r="G225" s="15"/>
-      <c r="H225" s="15"/>
+      <c r="H225" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I225" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J225" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J225" s="8"/>
       <c r="K225" s="15"/>
       <c r="L225" s="15"/>
     </row>
-    <row r="226" spans="2:12" ht="13">
+    <row r="226" spans="1:12" ht="13">
+      <c r="A226" s="4"/>
       <c r="B226" s="16" t="s">
         <v>8</v>
       </c>
@@ -6612,22 +6856,23 @@
         <v>235</v>
       </c>
       <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="17" t="s">
+      <c r="E226" s="17" t="s">
         <v>243</v>
       </c>
+      <c r="F226" s="17"/>
       <c r="G226" s="17"/>
-      <c r="H226" s="17"/>
+      <c r="H226" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I226" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J226" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J226" s="4"/>
       <c r="K226" s="17"/>
       <c r="L226" s="17"/>
     </row>
-    <row r="227" spans="2:12" ht="13">
+    <row r="227" spans="1:12" ht="13">
+      <c r="A227" s="8"/>
       <c r="B227" s="14" t="s">
         <v>3</v>
       </c>
@@ -6635,22 +6880,23 @@
         <v>235</v>
       </c>
       <c r="D227" s="6"/>
-      <c r="E227" s="6"/>
-      <c r="F227" s="15" t="s">
+      <c r="E227" s="15" t="s">
         <v>244</v>
       </c>
+      <c r="F227" s="15"/>
       <c r="G227" s="15"/>
-      <c r="H227" s="15"/>
+      <c r="H227" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I227" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J227" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J227" s="8"/>
       <c r="K227" s="15"/>
       <c r="L227" s="15"/>
     </row>
-    <row r="228" spans="2:12" ht="13">
+    <row r="228" spans="1:12" ht="13">
+      <c r="A228" s="4"/>
       <c r="B228" s="16" t="s">
         <v>3</v>
       </c>
@@ -6658,22 +6904,23 @@
         <v>235</v>
       </c>
       <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
-      <c r="F228" s="17" t="s">
+      <c r="E228" s="17" t="s">
         <v>245</v>
       </c>
+      <c r="F228" s="17"/>
       <c r="G228" s="17"/>
-      <c r="H228" s="17"/>
+      <c r="H228" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I228" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J228" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J228" s="4"/>
       <c r="K228" s="17"/>
       <c r="L228" s="17"/>
     </row>
-    <row r="229" spans="2:12" ht="13">
+    <row r="229" spans="1:12" ht="13">
+      <c r="A229" s="8"/>
       <c r="B229" s="14" t="s">
         <v>20</v>
       </c>
@@ -6681,22 +6928,23 @@
         <v>235</v>
       </c>
       <c r="D229" s="6"/>
-      <c r="E229" s="6"/>
-      <c r="F229" s="15" t="s">
+      <c r="E229" s="15" t="s">
         <v>246</v>
       </c>
+      <c r="F229" s="15"/>
       <c r="G229" s="15"/>
-      <c r="H229" s="15"/>
+      <c r="H229" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I229" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J229" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J229" s="8"/>
       <c r="K229" s="15"/>
       <c r="L229" s="15"/>
     </row>
-    <row r="230" spans="2:12" ht="13">
+    <row r="230" spans="1:12" ht="13">
+      <c r="A230" s="4"/>
       <c r="B230" s="16" t="s">
         <v>20</v>
       </c>
@@ -6704,22 +6952,23 @@
         <v>235</v>
       </c>
       <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
-      <c r="F230" s="17" t="s">
+      <c r="E230" s="17" t="s">
         <v>247</v>
       </c>
+      <c r="F230" s="17"/>
       <c r="G230" s="17"/>
-      <c r="H230" s="17"/>
+      <c r="H230" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I230" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J230" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J230" s="4"/>
       <c r="K230" s="17"/>
       <c r="L230" s="17"/>
     </row>
-    <row r="231" spans="2:12" ht="13">
+    <row r="231" spans="1:12" ht="13">
+      <c r="A231" s="8"/>
       <c r="B231" s="14" t="s">
         <v>20</v>
       </c>
@@ -6727,22 +6976,23 @@
         <v>235</v>
       </c>
       <c r="D231" s="6"/>
-      <c r="E231" s="6"/>
-      <c r="F231" s="15" t="s">
+      <c r="E231" s="15" t="s">
         <v>248</v>
       </c>
+      <c r="F231" s="15"/>
       <c r="G231" s="15"/>
-      <c r="H231" s="15"/>
+      <c r="H231" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I231" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J231" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J231" s="8"/>
       <c r="K231" s="15"/>
       <c r="L231" s="15"/>
     </row>
-    <row r="232" spans="2:12" ht="13">
+    <row r="232" spans="1:12" ht="13">
+      <c r="A232" s="4"/>
       <c r="B232" s="16" t="s">
         <v>20</v>
       </c>
@@ -6750,22 +7000,23 @@
         <v>235</v>
       </c>
       <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="17" t="s">
+      <c r="E232" s="17" t="s">
         <v>249</v>
       </c>
+      <c r="F232" s="17"/>
       <c r="G232" s="17"/>
-      <c r="H232" s="17"/>
+      <c r="H232" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I232" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J232" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J232" s="4"/>
       <c r="K232" s="17"/>
       <c r="L232" s="17"/>
     </row>
-    <row r="233" spans="2:12" ht="13">
+    <row r="233" spans="1:12" ht="13">
+      <c r="A233" s="8"/>
       <c r="B233" s="14" t="s">
         <v>20</v>
       </c>
@@ -6773,22 +7024,23 @@
         <v>235</v>
       </c>
       <c r="D233" s="6"/>
-      <c r="E233" s="6"/>
-      <c r="F233" s="15" t="s">
+      <c r="E233" s="15" t="s">
         <v>250</v>
       </c>
+      <c r="F233" s="15"/>
       <c r="G233" s="15"/>
-      <c r="H233" s="15"/>
+      <c r="H233" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I233" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J233" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J233" s="8"/>
       <c r="K233" s="15"/>
       <c r="L233" s="15"/>
     </row>
-    <row r="234" spans="2:12" ht="13">
+    <row r="234" spans="1:12" ht="13">
+      <c r="A234" s="4"/>
       <c r="B234" s="16" t="s">
         <v>20</v>
       </c>
@@ -6796,22 +7048,23 @@
         <v>235</v>
       </c>
       <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="17" t="s">
+      <c r="E234" s="17" t="s">
         <v>251</v>
       </c>
+      <c r="F234" s="17"/>
       <c r="G234" s="17"/>
-      <c r="H234" s="17"/>
+      <c r="H234" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I234" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J234" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J234" s="4"/>
       <c r="K234" s="17"/>
       <c r="L234" s="17"/>
     </row>
-    <row r="235" spans="2:12" ht="13">
+    <row r="235" spans="1:12" ht="13">
+      <c r="A235" s="8"/>
       <c r="B235" s="14" t="s">
         <v>20</v>
       </c>
@@ -6819,22 +7072,23 @@
         <v>235</v>
       </c>
       <c r="D235" s="6"/>
-      <c r="E235" s="6"/>
-      <c r="F235" s="15" t="s">
+      <c r="E235" s="15" t="s">
         <v>252</v>
       </c>
+      <c r="F235" s="15"/>
       <c r="G235" s="15"/>
-      <c r="H235" s="15"/>
+      <c r="H235" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I235" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J235" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J235" s="8"/>
       <c r="K235" s="15"/>
       <c r="L235" s="15"/>
     </row>
-    <row r="236" spans="2:12" ht="13">
+    <row r="236" spans="1:12" ht="13">
+      <c r="A236" s="4"/>
       <c r="B236" s="16" t="s">
         <v>20</v>
       </c>
@@ -6842,22 +7096,23 @@
         <v>235</v>
       </c>
       <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="17" t="s">
+      <c r="E236" s="17" t="s">
         <v>253</v>
       </c>
+      <c r="F236" s="17"/>
       <c r="G236" s="17"/>
-      <c r="H236" s="17"/>
+      <c r="H236" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I236" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J236" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J236" s="4"/>
       <c r="K236" s="17"/>
       <c r="L236" s="17"/>
     </row>
-    <row r="237" spans="2:12" ht="13">
+    <row r="237" spans="1:12" ht="13">
+      <c r="A237" s="8"/>
       <c r="B237" s="14" t="s">
         <v>20</v>
       </c>
@@ -6865,22 +7120,23 @@
         <v>235</v>
       </c>
       <c r="D237" s="6"/>
-      <c r="E237" s="6"/>
-      <c r="F237" s="15" t="s">
+      <c r="E237" s="15" t="s">
         <v>254</v>
       </c>
+      <c r="F237" s="15"/>
       <c r="G237" s="15"/>
-      <c r="H237" s="15"/>
+      <c r="H237" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I237" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J237" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J237" s="8"/>
       <c r="K237" s="15"/>
       <c r="L237" s="15"/>
     </row>
-    <row r="238" spans="2:12" ht="13">
+    <row r="238" spans="1:12" ht="13">
+      <c r="A238" s="4"/>
       <c r="B238" s="16" t="s">
         <v>20</v>
       </c>
@@ -6888,22 +7144,23 @@
         <v>235</v>
       </c>
       <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="17" t="s">
+      <c r="E238" s="17" t="s">
         <v>255</v>
       </c>
+      <c r="F238" s="17"/>
       <c r="G238" s="17"/>
-      <c r="H238" s="17"/>
+      <c r="H238" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I238" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J238" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J238" s="4"/>
       <c r="K238" s="17"/>
       <c r="L238" s="17"/>
     </row>
-    <row r="239" spans="2:12" ht="13">
+    <row r="239" spans="1:12" ht="13">
+      <c r="A239" s="8"/>
       <c r="B239" s="14" t="s">
         <v>20</v>
       </c>
@@ -6911,22 +7168,23 @@
         <v>235</v>
       </c>
       <c r="D239" s="6"/>
-      <c r="E239" s="6"/>
-      <c r="F239" s="15" t="s">
+      <c r="E239" s="15" t="s">
         <v>256</v>
       </c>
+      <c r="F239" s="15"/>
       <c r="G239" s="15"/>
-      <c r="H239" s="15"/>
+      <c r="H239" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I239" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J239" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J239" s="8"/>
       <c r="K239" s="15"/>
       <c r="L239" s="15"/>
     </row>
-    <row r="240" spans="2:12" ht="13">
+    <row r="240" spans="1:12" ht="13">
+      <c r="A240" s="4"/>
       <c r="B240" s="16" t="s">
         <v>20</v>
       </c>
@@ -6934,22 +7192,23 @@
         <v>235</v>
       </c>
       <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="17" t="s">
+      <c r="E240" s="17" t="s">
         <v>257</v>
       </c>
+      <c r="F240" s="17"/>
       <c r="G240" s="17"/>
-      <c r="H240" s="17"/>
+      <c r="H240" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I240" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J240" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J240" s="4"/>
       <c r="K240" s="17"/>
       <c r="L240" s="17"/>
     </row>
-    <row r="241" spans="2:28" ht="14">
+    <row r="241" spans="1:28" ht="14">
+      <c r="A241" s="8"/>
       <c r="B241" s="14" t="s">
         <v>8</v>
       </c>
@@ -6957,22 +7216,23 @@
         <v>258</v>
       </c>
       <c r="D241" s="15"/>
-      <c r="E241" s="15"/>
-      <c r="F241" s="8" t="s">
+      <c r="E241" s="8" t="s">
         <v>259</v>
       </c>
+      <c r="F241" s="8"/>
       <c r="G241" s="8"/>
-      <c r="H241" s="8"/>
+      <c r="H241" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I241" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J241" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J241" s="8"/>
       <c r="K241" s="15"/>
       <c r="L241" s="15"/>
     </row>
-    <row r="242" spans="2:28" ht="14">
+    <row r="242" spans="1:28" ht="14">
+      <c r="A242" s="4"/>
       <c r="B242" s="16" t="s">
         <v>8</v>
       </c>
@@ -6980,22 +7240,23 @@
         <v>258</v>
       </c>
       <c r="D242" s="17"/>
-      <c r="E242" s="17"/>
-      <c r="F242" s="4" t="s">
+      <c r="E242" s="4" t="s">
         <v>260</v>
       </c>
+      <c r="F242" s="4"/>
       <c r="G242" s="4"/>
-      <c r="H242" s="4"/>
+      <c r="H242" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I242" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J242" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J242" s="4"/>
       <c r="K242" s="17"/>
       <c r="L242" s="17"/>
     </row>
-    <row r="243" spans="2:28" ht="14">
+    <row r="243" spans="1:28" ht="14">
+      <c r="A243" s="8"/>
       <c r="B243" s="14" t="s">
         <v>8</v>
       </c>
@@ -7003,22 +7264,23 @@
         <v>258</v>
       </c>
       <c r="D243" s="15"/>
-      <c r="E243" s="15"/>
-      <c r="F243" s="8" t="s">
+      <c r="E243" s="8" t="s">
         <v>261</v>
       </c>
+      <c r="F243" s="8"/>
       <c r="G243" s="8"/>
-      <c r="H243" s="8"/>
+      <c r="H243" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I243" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J243" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J243" s="8"/>
       <c r="K243" s="15"/>
       <c r="L243" s="15"/>
     </row>
-    <row r="244" spans="2:28" ht="14">
+    <row r="244" spans="1:28" ht="14">
+      <c r="A244" s="4"/>
       <c r="B244" s="16" t="s">
         <v>8</v>
       </c>
@@ -7026,22 +7288,23 @@
         <v>258</v>
       </c>
       <c r="D244" s="17"/>
-      <c r="E244" s="17"/>
-      <c r="F244" s="4" t="s">
+      <c r="E244" s="4" t="s">
         <v>262</v>
       </c>
+      <c r="F244" s="4"/>
       <c r="G244" s="4"/>
-      <c r="H244" s="4"/>
+      <c r="H244" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I244" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J244" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J244" s="4"/>
       <c r="K244" s="17"/>
       <c r="L244" s="17"/>
     </row>
-    <row r="245" spans="2:28" ht="14">
+    <row r="245" spans="1:28" ht="14">
+      <c r="A245" s="8"/>
       <c r="B245" s="14" t="s">
         <v>8</v>
       </c>
@@ -7049,22 +7312,23 @@
         <v>258</v>
       </c>
       <c r="D245" s="15"/>
-      <c r="E245" s="15"/>
-      <c r="F245" s="8" t="s">
+      <c r="E245" s="8" t="s">
         <v>263</v>
       </c>
+      <c r="F245" s="8"/>
       <c r="G245" s="8"/>
-      <c r="H245" s="8"/>
+      <c r="H245" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I245" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J245" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J245" s="8"/>
       <c r="K245" s="15"/>
       <c r="L245" s="15"/>
     </row>
-    <row r="246" spans="2:28" ht="14">
+    <row r="246" spans="1:28" ht="14">
+      <c r="A246" s="4"/>
       <c r="B246" s="16" t="s">
         <v>8</v>
       </c>
@@ -7072,22 +7336,23 @@
         <v>258</v>
       </c>
       <c r="D246" s="17"/>
-      <c r="E246" s="17"/>
-      <c r="F246" s="4" t="s">
+      <c r="E246" s="4" t="s">
         <v>264</v>
       </c>
+      <c r="F246" s="4"/>
       <c r="G246" s="4"/>
-      <c r="H246" s="4"/>
+      <c r="H246" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I246" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J246" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J246" s="4"/>
       <c r="K246" s="17"/>
       <c r="L246" s="17"/>
     </row>
-    <row r="247" spans="2:28" ht="14">
+    <row r="247" spans="1:28" ht="14">
+      <c r="A247" s="8"/>
       <c r="B247" s="14" t="s">
         <v>8</v>
       </c>
@@ -7095,22 +7360,23 @@
         <v>258</v>
       </c>
       <c r="D247" s="15"/>
-      <c r="E247" s="15"/>
-      <c r="F247" s="8" t="s">
+      <c r="E247" s="8" t="s">
         <v>265</v>
       </c>
+      <c r="F247" s="8"/>
       <c r="G247" s="8"/>
-      <c r="H247" s="8"/>
+      <c r="H247" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I247" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J247" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J247" s="8"/>
       <c r="K247" s="15"/>
       <c r="L247" s="15"/>
     </row>
-    <row r="248" spans="2:28" ht="14">
+    <row r="248" spans="1:28" ht="14">
+      <c r="A248" s="4"/>
       <c r="B248" s="16" t="s">
         <v>8</v>
       </c>
@@ -7118,22 +7384,23 @@
         <v>258</v>
       </c>
       <c r="D248" s="17"/>
-      <c r="E248" s="17"/>
-      <c r="F248" s="4" t="s">
+      <c r="E248" s="4" t="s">
         <v>266</v>
       </c>
+      <c r="F248" s="4"/>
       <c r="G248" s="4"/>
-      <c r="H248" s="4"/>
+      <c r="H248" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I248" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="J248" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J248" s="4"/>
       <c r="K248" s="17"/>
       <c r="L248" s="17"/>
     </row>
-    <row r="249" spans="2:28" ht="14">
+    <row r="249" spans="1:28" ht="14">
+      <c r="A249" s="8"/>
       <c r="B249" s="14" t="s">
         <v>8</v>
       </c>
@@ -7141,22 +7408,23 @@
         <v>258</v>
       </c>
       <c r="D249" s="15"/>
-      <c r="E249" s="15"/>
-      <c r="F249" s="8" t="s">
+      <c r="E249" s="8" t="s">
         <v>267</v>
       </c>
+      <c r="F249" s="8"/>
       <c r="G249" s="8"/>
-      <c r="H249" s="8"/>
+      <c r="H249" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I249" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J249" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J249" s="8"/>
       <c r="K249" s="15"/>
       <c r="L249" s="15"/>
     </row>
-    <row r="250" spans="2:28" ht="14">
+    <row r="250" spans="1:28" ht="14">
+      <c r="A250" s="4"/>
       <c r="B250" s="16" t="s">
         <v>8</v>
       </c>
@@ -7164,22 +7432,23 @@
         <v>258</v>
       </c>
       <c r="D250" s="17"/>
-      <c r="E250" s="17"/>
-      <c r="F250" s="4" t="s">
+      <c r="E250" s="4" t="s">
         <v>268</v>
       </c>
+      <c r="F250" s="4"/>
       <c r="G250" s="4"/>
-      <c r="H250" s="4"/>
+      <c r="H250" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I250" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J250" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J250" s="4"/>
       <c r="K250" s="17"/>
       <c r="L250" s="17"/>
     </row>
-    <row r="251" spans="2:28" ht="14">
+    <row r="251" spans="1:28" ht="14">
+      <c r="A251" s="8"/>
       <c r="B251" s="14" t="s">
         <v>8</v>
       </c>
@@ -7187,22 +7456,23 @@
         <v>258</v>
       </c>
       <c r="D251" s="15"/>
-      <c r="E251" s="15"/>
-      <c r="F251" s="8" t="s">
+      <c r="E251" s="8" t="s">
         <v>269</v>
       </c>
+      <c r="F251" s="8"/>
       <c r="G251" s="8"/>
-      <c r="H251" s="8"/>
+      <c r="H251" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I251" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J251" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J251" s="8"/>
       <c r="K251" s="15"/>
       <c r="L251" s="15"/>
     </row>
-    <row r="252" spans="2:28" ht="14">
+    <row r="252" spans="1:28" ht="14">
+      <c r="A252" s="4"/>
       <c r="B252" s="16" t="s">
         <v>8</v>
       </c>
@@ -7210,22 +7480,23 @@
         <v>258</v>
       </c>
       <c r="D252" s="17"/>
-      <c r="E252" s="17"/>
-      <c r="F252" s="4" t="s">
+      <c r="E252" s="4" t="s">
         <v>270</v>
       </c>
+      <c r="F252" s="4"/>
       <c r="G252" s="4"/>
-      <c r="H252" s="4"/>
+      <c r="H252" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I252" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="J252" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="J252" s="4"/>
       <c r="K252" s="17"/>
       <c r="L252" s="17"/>
     </row>
-    <row r="253" spans="2:28" ht="14">
+    <row r="253" spans="1:28" ht="14">
+      <c r="A253" s="8"/>
       <c r="B253" s="14" t="s">
         <v>8</v>
       </c>
@@ -7233,22 +7504,23 @@
         <v>258</v>
       </c>
       <c r="D253" s="15"/>
-      <c r="E253" s="15"/>
-      <c r="F253" s="8" t="s">
+      <c r="E253" s="8" t="s">
         <v>271</v>
       </c>
+      <c r="F253" s="8"/>
       <c r="G253" s="8"/>
-      <c r="H253" s="8"/>
+      <c r="H253" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="I253" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J253" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="J253" s="8"/>
       <c r="K253" s="15"/>
       <c r="L253" s="15"/>
     </row>
-    <row r="254" spans="2:28" ht="14">
+    <row r="254" spans="1:28" ht="14">
+      <c r="A254" s="4"/>
       <c r="B254" s="16" t="s">
         <v>8</v>
       </c>
@@ -7256,18 +7528,18 @@
         <v>13</v>
       </c>
       <c r="D254" s="17"/>
-      <c r="E254" s="17"/>
-      <c r="F254" s="4" t="s">
+      <c r="E254" s="4" t="s">
         <v>272</v>
       </c>
+      <c r="F254" s="4"/>
       <c r="G254" s="4"/>
-      <c r="H254" s="4"/>
+      <c r="H254" s="18" t="s">
+        <v>6</v>
+      </c>
       <c r="I254" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J254" s="18" t="s">
-        <v>6</v>
-      </c>
+      <c r="J254" s="4"/>
       <c r="K254" s="17"/>
       <c r="L254" s="17"/>
       <c r="M254" s="19"/>
@@ -7287,7 +7559,8 @@
       <c r="AA254" s="19"/>
       <c r="AB254" s="19"/>
     </row>
-    <row r="255" spans="2:28" ht="14">
+    <row r="255" spans="1:28" ht="14">
+      <c r="A255" s="8"/>
       <c r="B255" s="14" t="s">
         <v>8</v>
       </c>
@@ -7295,18 +7568,18 @@
         <v>13</v>
       </c>
       <c r="D255" s="15"/>
-      <c r="E255" s="15"/>
-      <c r="F255" s="8" t="s">
+      <c r="E255" s="8" t="s">
         <v>273</v>
       </c>
+      <c r="F255" s="8"/>
       <c r="G255" s="8"/>
-      <c r="H255" s="8"/>
+      <c r="H255" s="18" t="s">
+        <v>6</v>
+      </c>
       <c r="I255" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J255" s="18" t="s">
-        <v>6</v>
-      </c>
+      <c r="J255" s="8"/>
       <c r="K255" s="15"/>
       <c r="L255" s="15"/>
       <c r="M255" s="19"/>
@@ -7326,7 +7599,8 @@
       <c r="AA255" s="19"/>
       <c r="AB255" s="19"/>
     </row>
-    <row r="256" spans="2:28" ht="56">
+    <row r="256" spans="1:28" ht="56">
+      <c r="A256" s="4"/>
       <c r="B256" s="14" t="s">
         <v>8</v>
       </c>
@@ -7334,18 +7608,18 @@
         <v>13</v>
       </c>
       <c r="D256" s="15"/>
-      <c r="E256" s="15"/>
-      <c r="F256" s="8" t="s">
+      <c r="E256" s="8" t="s">
         <v>274</v>
       </c>
+      <c r="F256" s="8"/>
       <c r="G256" s="8"/>
-      <c r="H256" s="8"/>
+      <c r="H256" s="18" t="s">
+        <v>6</v>
+      </c>
       <c r="I256" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J256" s="18" t="s">
-        <v>6</v>
-      </c>
+      <c r="J256" s="4"/>
       <c r="K256" s="15"/>
       <c r="L256" s="15"/>
     </row>
@@ -10279,21 +10553,21 @@
     </row>
   </sheetData>
   <autoFilter ref="B1:K253" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="J2:J256">
+  <conditionalFormatting sqref="H2:H256">
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Funciona">
-      <formula>NOT(ISERROR(SEARCH("Funciona",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Funciona",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Falla">
-      <formula>NOT(ISERROR(SEARCH("Falla",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Falla",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH("N/A",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("N/A",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Pendiente">
-      <formula>NOT(ISERROR(SEARCH("Pendiente",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Pendiente",H2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Por ejecutar">
-      <formula>NOT(ISERROR(SEARCH("Por ejecutar",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Por ejecutar",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -10301,7 +10575,7 @@
       <formula1>"Acceso,Buscador,Control Compras,Control Parental,Navegación,NPVR,Perfiles,Rep. Canal Líneal,Reproducción,TimeShift,Transacción,Claro Música,Trickplay,Social y Settings"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J256" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H256" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Funciona,Falla nueva,Falla persiste,N/A,Pendiente,Por ejecutar,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
